--- a/grok/Book_PDF_File_Coverage_Grok.xlsx
+++ b/grok/Book_PDF_File_Coverage_Grok.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Src_Package_Coverage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File_Coverage_All" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOT_IN_BOOK_Src" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CITED_Src" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book_Citations_Raw" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Src_Package_Coverage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="File_Coverage_All" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NOT_IN_BOOK_Src" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CITED_Src" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Book_Citations_Raw" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Legend" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'File_Coverage_All'!$A$1:$I$951</definedName>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -95,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -112,6 +115,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,11 +566,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -661,11 +660,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -690,7 +684,6 @@
       <c r="B15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -701,7 +694,6 @@
       <c r="B16" t="n">
         <v>302</v>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -729,12 +721,6 @@
           <t>1.3%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -742,8 +728,6 @@
           <t>INTERPRETATION (src dormancy_hint counts)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -849,11 +833,6 @@
           <t>Under archive/</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2407,7 +2386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I951"/>
+  <dimension ref="A1:J951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2467,6 +2446,11 @@
           <t>referred_files</t>
         </is>
       </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Story_IDs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2510,6 +2494,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>STORY-18.2; STORY-18.5; STORY-18.7; STORY-20.5; STORY-25.20; STORY-30.5; STORY-33.1; STORY-57.3</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2553,6 +2542,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>STORY-19.2; STORY-19.6; STORY-20.16; STORY-31.26; STORY-33.5; STORY-41.24; STORY-41.52</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2596,6 +2590,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-31.16; STORY-31.19; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2641,6 +2640,11 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>src/multi_llm/discussion.py</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>STORY-19.10; STORY-41.1; STORY-41.36</t>
         </is>
       </c>
     </row>
@@ -2854,6 +2858,11 @@
           <t>src/features/feature_pipeline.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>STORY-14.7; STORY-20.12; STORY-41.44</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2897,6 +2906,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>STORY-14.7</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2991,6 +3005,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/research/contracts.py; src/research/measurement/forward_walk.py</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>STORY-15.1; STORY-30.3; STORY-37.3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3132,6 +3151,11 @@
           <t>src/replay/timing_reconstructor.py; src/replay/timing_advisor.py</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>STORY-41.59</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3175,6 +3199,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>STORY-41.24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3218,6 +3247,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3308,6 +3342,11 @@
           <t>src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-18.12; STORY-25.32; STORY-35.2; STORY-37.12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3355,6 +3394,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>STORY-18.2; STORY-20.5; STORY-30.5; STORY-33.1; STORY-36.9; STORY-41.4; STORY-41.10</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3449,6 +3493,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/registry/__init__.py; src/runtime/backtest_v2.p</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>STORY-20.19</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3496,6 +3545,11 @@
           <t>src/config_layer/production_config.py; src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py; src/runtime/crt_fail_reason_counters.py</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3539,6 +3593,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3727,6 +3786,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py; src/runtime/crt_baseline_trace.py</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>STORY-31.6</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3864,6 +3928,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4099,6 +4168,11 @@
           <t>src/data_ingestion/xauusd_phase1_candidate.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>STORY-25.8</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4193,6 +4267,11 @@
           <t>src/features/feature_schema.py; src/features/feature_pipeline.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>STORY-18.3; STORY-36.16</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4240,6 +4319,11 @@
           <t>src/features/feature_schema.py; src/features/formula_registry.py</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>STORY-25.5; STORY-25.16; STORY-31.18</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4287,6 +4371,11 @@
           <t>src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>STORY-25.3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4334,6 +4423,11 @@
           <t>src/features/feature_pipeline.py; src/features/__init__.py; src/features/derived_math.py</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>STORY-25.3</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4428,6 +4522,11 @@
           <t>src/features/feature_pipeline.py; src/engines/__init__.py; src/engines/crt_engine.py</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>STORY-41.26</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4475,6 +4574,11 @@
           <t>src/features/registry/__init__.py</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-25.5; STORY-25.12; STORY-25.15; STORY-25.22; STORY-31.23; STORY-33.1; STORY-36.2; STORY-36.23; STORY-41.26</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4800,6 +4904,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4929,6 +5038,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>STORY-41.50</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5019,6 +5133,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>STORY-20.28; STORY-33.5; STORY-41.13; STORY-41.52</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5066,6 +5185,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5109,6 +5233,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>STORY-19.2; STORY-41.24</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5195,6 +5324,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>STORY-25.16; STORY-35.2; STORY-41.1; STORY-41.24</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5242,6 +5376,11 @@
           <t>src/control_plane/registry.py</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>STORY-15.1; STORY-18.12; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5289,6 +5428,11 @@
           <t>src/governance/script_registry.py; src/utils/jsonl_writer.py</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>STORY-20.10; STORY-31.22; STORY-33.5; STORY-33.8; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5375,6 +5519,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>STORY-33.1; STORY-41.24</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5516,6 +5665,11 @@
           <t>src/config_layer/production_config.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>STORY-25.20; STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5610,6 +5764,11 @@
           <t>src/features/__init__.py; src/features/candle_math.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>STORY-41.17</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5657,6 +5816,11 @@
           <t>src/features/model_evidence.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py; src/core/collector.py</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>STORY-31.3</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5704,6 +5868,11 @@
           <t>src/governance/module_attribution.py; src/governance/module_census.py</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>STORY-33.8</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5747,6 +5916,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>STORY-41.17</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5841,6 +6015,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>STORY-25.29</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5888,6 +6067,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>STORY-25.29</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5935,6 +6119,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>STORY-25.29; STORY-41.46</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5978,6 +6167,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>STORY-41.50</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6025,6 +6219,11 @@
           <t>src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>STORY-25.29; STORY-41.46</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6072,6 +6271,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>STORY-41.46</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6119,6 +6323,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>STORY-25.29; STORY-41.46</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6166,6 +6375,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>STORY-41.46</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6256,6 +6470,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>STORY-25.5</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6303,6 +6522,11 @@
           <t>src/data_ingestion/xauusd_phase1_candidate.py; src/features/feature_pipeline.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>STORY-18.3</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6491,6 +6715,11 @@
           <t>src/research/process_characterization.py; src/runtime/backtest_v2.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6581,6 +6810,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>STORY-41.34</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6667,6 +6901,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6710,6 +6949,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>STORY-41.4</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6757,6 +7001,11 @@
           <t>src/charts/__init__.py; src/charts/chart_series.py; src/charts/crt_overlay.py; src/charts/render.py</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>STORY-41.32</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6804,6 +7053,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>STORY-36.16</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6851,6 +7105,11 @@
           <t>src/config_layer/rr/rr_pattern_miner.py; src/config_layer/rr/rr_fusion.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>STORY-20.22; STORY-37.1; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6898,6 +7157,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/features/__init__.py; src/features/candle_math.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>STORY-51.3</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6945,6 +7209,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>STORY-20.19</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7039,6 +7308,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/msip/disagreement.py; src/msip/interpretation_config.py; src/msip/shadow_emitter.py</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>STORY-51.3</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7180,6 +7454,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7227,6 +7506,11 @@
           <t>src/governance/script_census.py</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>STORY-11.16; STORY-14.2; STORY-25.16; STORY-31.6; STORY-31.14; STORY-31.22; STORY-33.5; STORY-33.8; STORY-41.31; STORY-41.40</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7321,6 +7605,11 @@
           <t>src/features/__init__.py; src/features/candle_math.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>STORY-41.16; STORY-41.17</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7411,6 +7700,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>STORY-33.16</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7458,6 +7752,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py; src/features/__init__.py; src/features/broker_clock.py</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>STORY-20.19</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7552,6 +7851,11 @@
           <t>src/runtime/backtest_v2.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>STORY-23.8; STORY-25.23; STORY-33.2; STORY-33.18</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7599,6 +7903,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>STORY-20.22; STORY-36.3</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7642,6 +7951,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7732,6 +8046,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>STORY-18.8; STORY-41.4</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7967,6 +8286,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/core/engine_runner.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>STORY-20.12; STORY-20.19</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8108,6 +8432,11 @@
           <t>src/features/feature_schema.py; src/research/zone_label_audit.py; scripts/research/zone_label_audit.py; src/research/zone_mapping/historical_zone_mapper.py</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>STORY-37.8</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8155,6 +8484,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/schema_validator.py</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>STORY-37.12; STORY-37.13</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8200,6 +8534,11 @@
       <c r="I126" s="2" t="inlineStr">
         <is>
           <t>src/features/feature_schema.py</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>STORY-37.2; STORY-37.8</t>
         </is>
       </c>
     </row>
@@ -8241,6 +8580,11 @@
           <t>src/utils/integrity_events.py; src/core/model_registry.py</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>STORY-18.1; STORY-18.12; STORY-35.2; STORY-37.10; STORY-37.12; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8280,6 +8624,11 @@
           <t>src/config_layer/config_builder.py</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8315,6 +8664,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-20.22; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8502,6 +8856,11 @@
           <t>src/control_plane/server.py</t>
         </is>
       </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>STORY-6.1; STORY-18.1; STORY-18.12; STORY-35.2; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8537,6 +8896,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8576,6 +8940,11 @@
           <t>src/config_layer/rr/rr_dataset_builder.py; src/core/model_registry.py</t>
         </is>
       </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-18.11; STORY-18.12; STORY-35.2; STORY-37.13</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8615,6 +8984,11 @@
           <t>src/features/dataset_validator.py</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8720,6 +9094,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8868,6 +9247,11 @@
           <t>src/config_layer/production_config.py; src/data_ingestion/dataset_integrity.py; src/data_ingestion/session_autoderive.py; src/inout/mt5_candle_fetcher.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>STORY-31.13</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8907,6 +9291,11 @@
           <t>src/inout/alphavantage_candle_fetcher.py</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-29.1; STORY-29.7</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8946,6 +9335,11 @@
           <t>src/inout/hummingbot_candle_fetcher.py</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-20.31; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8985,6 +9379,11 @@
           <t>src/inout/mt5_candle_fetcher.py</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>STORY-25.13</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9020,6 +9419,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>STORY-3.1; STORY-3.2; STORY-10.3; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9055,6 +9459,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9094,6 +9503,11 @@
           <t>src/inout/perp_funding_fetcher.py</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>STORY-29.1</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9133,6 +9547,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9168,6 +9587,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>STORY-6.3; STORY-18.1; STORY-18.12; STORY-25.30</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9273,6 +9697,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>STORY-18.1; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9417,6 +9846,11 @@
           <t>src/retrieval/__init__.py; src/retrieval/config.py; src/retrieval/retriever.py</t>
         </is>
       </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>STORY-19.3; STORY-25.24</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9456,6 +9890,11 @@
           <t>src/features/feature_schema.py; src/bitnet/model_contract.py</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>STORY-16.1; STORY-25.32; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9495,6 +9934,11 @@
           <t>src/bitnet/model_contract.py</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>STORY-25.32; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9534,6 +9978,11 @@
           <t>src/bitnet/model_contract.py</t>
         </is>
       </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>STORY-25.32; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9647,6 +10096,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>STORY-11.6</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9835,6 +10289,11 @@
           <t>(parse failed — imports unavailable)</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>STORY-20.20</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9882,6 +10341,11 @@
           <t>src/config_layer/state_topology.py</t>
         </is>
       </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>STORY-18.8</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9972,6 +10436,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>STORY-11.15; STORY-14.2; STORY-14.3; STORY-14.4; STORY-25.3; STORY-25.4; STORY-25.11; STORY-25.16; STORY-25.27; STORY-30.1; STORY-31.4; STORY-31.6; STORY-31.14; STORY-31.16; STORY-31.20; STORY-31.22; STORY-33.5; STORY-33.8; STORY-33.9; STORY-33.11; STORY-36.8; STORY-36.12; STORY-36.16; STORY-36.23; STORY-41.20; STORY-41.31; STORY-41.40; STORY-41.44</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10019,6 +10488,11 @@
           <t>src/governance/semantic_objects.py; src/governance/semantic_os.py</t>
         </is>
       </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>STORY-33.5; STORY-45.1</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10066,6 +10540,11 @@
           <t>src/config_layer/crt_config_provenance.py</t>
         </is>
       </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>STORY-33.10</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10109,6 +10588,11 @@
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>STORY-31.19; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10156,6 +10640,11 @@
           <t>src/governance/findings_export.py</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-20.10; STORY-20.25; STORY-21.1; STORY-33.5; STORY-36.8; STORY-36.12; STORY-36.15; STORY-36.16; STORY-41.4; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10203,6 +10692,11 @@
           <t>src/features/formula_registry.py</t>
         </is>
       </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>STORY-25.3</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10246,6 +10740,11 @@
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>STORY-25.3; STORY-31.18</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10293,6 +10792,11 @@
           <t>src/features/feature_schema.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-31.18; STORY-31.22</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10340,6 +10844,11 @@
           <t>src/governance/framework_registry.py</t>
         </is>
       </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>STORY-23.1; STORY-32.1</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10387,6 +10896,11 @@
           <t>src/governance/framework_registry.py</t>
         </is>
       </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>STORY-3.4; STORY-18.1; STORY-23.1; STORY-32.1</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10477,6 +10991,11 @@
           <t>src/governance/multi_strategy_validator.py; src/governance/promotion_manager.py</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-33.20</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10571,6 +11090,11 @@
           <t>src/governance/hypothesis_registry.py</t>
         </is>
       </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>STORY-21.1</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10618,6 +11142,11 @@
           <t>src/governance/framework_registry.py</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>STORY-3.3; STORY-18.1; STORY-21.1; STORY-23.1; STORY-32.1</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10665,6 +11194,11 @@
           <t>src/governance/script_registry.py</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-20.26; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10712,6 +11246,11 @@
           <t>src/governance/semantic_os.py; src/governance/semantic_query.py; src/governance/semantic_grounding.py</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>STORY-14.3; STORY-14.4; STORY-25.6; STORY-25.12; STORY-25.27; STORY-31.22; STORY-33.5; STORY-36.2; STORY-36.4; STORY-36.23; STORY-41.41; STORY-45.2</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10759,6 +11298,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>STORY-25.2</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10806,6 +11350,11 @@
           <t>src/data_ingestion/clock_detector.py; src/data_ingestion/clock_registry.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-25.25; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10935,6 +11484,11 @@
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>STORY-37.2</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10982,6 +11536,11 @@
           <t>src/governance/framework_registry.py</t>
         </is>
       </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-4.2; STORY-4.3; STORY-4.4; STORY-9.1; STORY-10.2; STORY-10.3; STORY-18.1; STORY-21.1; STORY-23.1; STORY-32.1</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -11029,6 +11588,11 @@
           <t>src/governance/hypothesis_registry.py</t>
         </is>
       </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>STORY-21.1</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11076,6 +11640,11 @@
           <t>src/governance/script_registry.py; src/governance/script_seed.py; src/utils/jsonl_writer.py</t>
         </is>
       </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>STORY-20.10; STORY-20.26; STORY-25.12; STORY-31.6; STORY-31.14; STORY-31.22; STORY-33.5; STORY-33.8; STORY-36.3; STORY-41.31; STORY-41.40</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -11123,6 +11692,11 @@
           <t>src/governance/semantic_os.py; src/governance/semantic_identity.py; src/governance/semantic_objects.py</t>
         </is>
       </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>STORY-31.19; STORY-31.22; STORY-31.23; STORY-33.5</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11217,6 +11791,11 @@
           <t>src/governance/framework_registry.py</t>
         </is>
       </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>STORY-23.1; STORY-32.1</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -11264,6 +11843,11 @@
           <t>src/validation_access/ladder.py; src/validation_access/surfaces.py</t>
         </is>
       </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>STORY-14.4</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -11309,6 +11893,11 @@
       <c r="I201" s="2" t="inlineStr">
         <is>
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>STORY-18.8</t>
         </is>
       </c>
     </row>
@@ -11346,6 +11935,11 @@
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11381,6 +11975,11 @@
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-41.55</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11416,6 +12015,11 @@
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-41.55</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -11455,6 +12059,11 @@
           <t>src/inout/live_rail/config.py; src/runtime/live_rail_orchestrator.py; src/inout/live_rail/ohlcv_replay_port.py</t>
         </is>
       </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>STORY-13.6; STORY-13.7; STORY-29.2; STORY-29.4; STORY-42.4</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11490,6 +12099,11 @@
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>STORY-16.5; STORY-18.12; STORY-19.4; STORY-20.5; STORY-20.29; STORY-20.30; STORY-20.31; STORY-21.3; STORY-23.3; STORY-23.7; STORY-23.8; STORY-26.1; STORY-27.2; STORY-29.6; STORY-29.7; STORY-33.2; STORY-33.15; STORY-33.18; STORY-35.2; STORY-36.11; STORY-37.1; STORY-37.5; STORY-37.6; STORY-37.11; STORY-37.12; STORY-41.51; STORY-41.56</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -11599,6 +12213,11 @@
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>STORY-14.3; STORY-14.4; STORY-18.8; STORY-20.11; STORY-20.13; STORY-20.14; STORY-20.27; STORY-25.1; STORY-25.4; STORY-25.9; STORY-25.12; STORY-25.16; STORY-25.20; STORY-25.24; STORY-31.11; STORY-31.15; STORY-31.22; STORY-33.5; STORY-33.9; STORY-36.7; STORY-41.31; STORY-41.40; STORY-41.41</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11634,6 +12253,11 @@
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>STORY-25.12</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -11669,6 +12293,11 @@
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>STORY-18.11</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11704,6 +12333,11 @@
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -11743,6 +12377,11 @@
           <t>src/utils/console_safe.py; src/utils/parquet_store.py</t>
         </is>
       </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>STORY-25.4; STORY-25.14; STORY-41.40; STORY-43.3; STORY-44.1</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -11778,6 +12417,11 @@
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>STORY-18.11</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -11813,6 +12457,11 @@
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>STORY-36.16; STORY-41.23; STORY-41.42</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -11852,6 +12501,11 @@
           <t>src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>STORY-30.2</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -11891,6 +12545,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -11926,6 +12585,11 @@
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -11961,6 +12625,11 @@
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -11996,6 +12665,11 @@
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -12035,6 +12709,11 @@
           <t>src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>STORY-25.32; STORY-35.1; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12109,6 +12788,11 @@
           <t>src/portfolio/replay.py</t>
         </is>
       </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12148,6 +12832,11 @@
           <t>src/retrieval/__init__.py; src/retrieval/config.py; src/retrieval/corpus.py; src/retrieval/retriever.py; src/retrieval/claude_integration.py</t>
         </is>
       </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-19.3; STORY-25.24; STORY-41.8</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -12195,6 +12884,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12238,6 +12932,11 @@
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -12285,6 +12984,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -12332,6 +13036,11 @@
           <t>src/engines/crt_engine.py; src/engines/heuristic_gaussian_engine.py; src/engines/rr_engine.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -12379,6 +13088,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12422,6 +13136,11 @@
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -12465,6 +13184,11 @@
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12508,6 +13232,11 @@
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -12551,6 +13280,11 @@
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>STORY-41.68</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -12598,6 +13332,11 @@
           <t>src/config_layer/production_config.py; src/research/config.py; src/research/provenance.py; src/research/qualification.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -12688,6 +13427,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -12735,6 +13479,11 @@
           <t>src/features/feature_schema.py; src/utils/console_safe.py; src/utils/run_manifest.py</t>
         </is>
       </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -12829,6 +13578,11 @@
           <t>src/bitnet/contract_c_trainer.py; src/bitnet/r25_kill_test.py</t>
         </is>
       </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>STORY-16.1</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -12876,6 +13630,11 @@
           <t>src/research/adapters/spine_signal_source.py</t>
         </is>
       </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>STORY-16.1; STORY-16.3; STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -12919,6 +13678,11 @@
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -12966,6 +13730,11 @@
           <t>src/research/qualification.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -13009,6 +13778,11 @@
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -13056,6 +13830,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/config.py; src/research/forensics.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -13103,6 +13882,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/features/crt_state_resolver.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/feature_sta</t>
         </is>
       </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>STORY-20.20; STORY-25.17; STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -13150,6 +13934,11 @@
           <t>src/research/zone_mapping/boundary_hypothesis_eval.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -13197,6 +13986,11 @@
           <t>src/research/clean_labels/builder.py; src/research/clean_labels/protocol.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -13244,6 +14038,11 @@
           <t>src/research/zone_mapping/crt_zone_crosstab.py; src/research/zone_mapping/historical_zone_mapper.py; src/research/zone_mapping/build_corpus_zone_map.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -13291,6 +14090,11 @@
           <t>src/research/zone_mapping/displacement_zone_event_study.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -13338,6 +14142,11 @@
           <t>src/research/episodes/projectors/detection.py; src/research/episodes/projectors/spine.py; src/research/episodes/protocol.py; src/research/episodes/store.py</t>
         </is>
       </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -13385,6 +14194,11 @@
           <t>src/research/zone_mapping/gaussian_delta_gap_eval.py</t>
         </is>
       </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -13432,6 +14246,11 @@
           <t>src/research/zone_mapping/gaussian_family_shadow_eval.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -13479,6 +14298,11 @@
           <t>src/research/zone_mapping/rare_zone_context_filter_eval.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -13526,6 +14350,11 @@
           <t>src/research/zone_mapping/rare_zone_detection_eval.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -13573,6 +14402,11 @@
           <t>src/research/zone_mapping/rare_zone_fa_characterization.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -13620,6 +14454,11 @@
           <t>src/research/resample.py; src/utils/console_safe.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>STORY-36.21</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -13667,6 +14506,11 @@
           <t>src/config_layer/rr/rr_dataset_builder.py; src/research/clean_labels/builder.py; src/research/clean_labels/protocol.py</t>
         </is>
       </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>STORY-25.37</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -13714,6 +14558,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/data_ingestion/xauusd_phase1_candidate.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/research/co</t>
         </is>
       </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -13761,6 +14610,11 @@
           <t>src/research/zone_mapping/build_corpus_zone_map.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -13808,6 +14662,11 @@
           <t>src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -13855,6 +14714,11 @@
           <t>src/data_ingestion/dataset_integrity.py; src/data_ingestion/ohlcv_schema.py; src/data_ingestion/xauusd_phase1_candidate.py; src/utils/run_manifest.py</t>
         </is>
       </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -13902,6 +14766,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>STORY-37.2; STORY-37.8</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -13945,6 +14814,11 @@
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>STORY-20.23; STORY-31.17; STORY-33.9</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -13988,6 +14862,11 @@
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr"/>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>STORY-33.9</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -14035,6 +14914,11 @@
           <t>src/runtime/backtest_v2.py; src/config_layer/config_builder.py</t>
         </is>
       </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>STORY-20.14</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -14082,6 +14966,11 @@
           <t>src/structure/predicates.py; src/features/feature_pipeline.py; src/features/crt_state_resolver.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -14129,6 +15018,11 @@
           <t>src/config_layer/config_builder.py; src/runtime/backtest_v2.py; src/features/crt_state_resolver.py; src/features/feature_schema.py; src/research/contracts.py; src/research/measurement/forward_walk.py;</t>
         </is>
       </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>STORY-20.26</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -14176,6 +15070,11 @@
           <t>src/features/feature_pipeline.py; src/features/crt_state_resolver.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>STORY-20.6; STORY-20.12; STORY-20.23; STORY-20.26; STORY-33.9; STORY-36.6</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -14219,6 +15118,11 @@
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>STORY-20.23</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -14309,6 +15213,11 @@
           <t>src/engines/heuristic_gaussian_engine.py; src/research/provenance.py; src/research/config.py; src/research/qualification.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>STORY-37.7</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -14356,6 +15265,11 @@
           <t>src/research/provenance.py; src/research/config.py; src/research/qualification.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>STORY-37.7</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -14403,6 +15317,11 @@
           <t>src/research/adapters/spine_signal_source.py</t>
         </is>
       </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>STORY-25.2</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -14450,6 +15369,11 @@
           <t>src/features/feature_schema.py; src/core/model_registry.py</t>
         </is>
       </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-16.4; STORY-18.11; STORY-18.12; STORY-18.13; STORY-35.2; STORY-37.2; STORY-37.3; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -14497,6 +15421,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>STORY-31.7; STORY-31.14; STORY-41.50</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -14544,6 +15473,11 @@
           <t>src/data_ingestion/ohlcv_schema.py; src/engines/crt_engine.py; src/engines/heuristic_gaussian_engine.py; src/engines/rr_engine.py; src/engines/scoring_engine.py; src/engines/zone_gate_engine.py; src/f</t>
         </is>
       </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -14591,6 +15525,11 @@
           <t>src/analytics/sl_tp_comparator.py; src/config_layer/production_config.py; src/config_layer/config_builder.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>STORY-15.2</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -14638,6 +15577,11 @@
           <t>src/config_layer/production_config.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/oracle/exit_analysis.py; src/research/oracle/labeler.py; src/research/oracle/multi_</t>
         </is>
       </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>STORY-41.11</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -14685,6 +15629,11 @@
           <t>src/features/registry/__init__.py</t>
         </is>
       </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -14732,6 +15681,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>STORY-18.13</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -14779,6 +15733,11 @@
           <t>src/features/feature_schema.py; src/research/contracts.py; src/research/measurement/forward_walk.py; src/research/zone_label_audit.py; scripts/research/zone_label_audit.py</t>
         </is>
       </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -14826,6 +15785,11 @@
           <t>src/research/adapters/spine_signal_source.py; src/core/engine_runner.py</t>
         </is>
       </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -14873,6 +15837,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -14967,6 +15936,11 @@
           <t>src/research/hypotheses/__init__.py; src/research/costs.py; src/research/exit_grid.py; src/research/registry.py; src/utils/console_safe.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>STORY-33.6; STORY-33.7</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -15014,6 +15988,11 @@
           <t>src/config_layer/production_config.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>STORY-31.6</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -15061,6 +16040,11 @@
           <t>src/runtime/backtest_v2.py; src/runtime/parent_crt_feed.py</t>
         </is>
       </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>STORY-25.27; STORY-31.6; STORY-31.8</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -15108,6 +16092,11 @@
           <t>src/research/ic002_entry_evolution/build_trajectories.py; src/research/ic002_entry_evolution/io_util.py; src/research/ic002_entry_evolution/schema.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>STORY-33.7</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -15155,6 +16144,11 @@
           <t>src/research/ic002_entry_evolution/evaluate_separation.py; src/research/ic002_entry_evolution/io_util.py; src/research/ic002_entry_evolution/schema.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>STORY-33.7</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -15202,6 +16196,11 @@
           <t>src/research/ic003_shapes/build_library.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>STORY-33.7</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -15249,6 +16248,11 @@
           <t>src/research/ic003b_sequence_geometry/build_all.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -15296,6 +16300,11 @@
           <t>src/research/ic002_entry_evolution/io_util.py; src/research/ic003b_sequence_geometry/summarize.py</t>
         </is>
       </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -15339,6 +16348,11 @@
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>STORY-30.6</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -15382,6 +16396,11 @@
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -15429,6 +16448,11 @@
           <t>src/config_layer/production_config.py; src/config_layer/config_builder.py; src/config_layer/execution_planner.py; src/core/ultron_risk_gate.py; src/core/ultron_risk_gate_wrapper.py; src/runtime/backte</t>
         </is>
       </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>STORY-23.7; STORY-30.6; STORY-31.23</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -15476,6 +16500,11 @@
           <t>src/research/candle_state/encoder.py; src/research/candle_state/info_robustness.py; src/research/candle_state/m5_incremental.py; src/research/candle_state/mtf_conjunction.py; src/research/candle_state</t>
         </is>
       </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -15523,6 +16552,11 @@
           <t>src/features/broker_clock.py; src/features/feature_pipeline.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>STORY-36.11</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -15570,6 +16604,11 @@
           <t>src/research/adapters/spine_signal_source.py; src/research/contracts.py; src/research/goal_alignment.py</t>
         </is>
       </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -15613,6 +16652,11 @@
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -15660,6 +16704,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-16.4; STORY-18.11; STORY-18.12; STORY-25.6; STORY-30.1; STORY-31.11; STORY-35.2; STORY-36.5; STORY-37.2; STORY-38.3; STORY-38.6; STORY-41.56; STORY-41.57</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -15707,6 +16756,11 @@
           <t>src/features/feature_schema.py; src/research/oracle/scan.py</t>
         </is>
       </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -15754,6 +16808,11 @@
           <t>src/config_layer/state_identity.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>STORY-14.4</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -15801,6 +16860,11 @@
           <t>src/data_ingestion/xauusd_phase1_candidate.py; src/charts/crt_overlay.py</t>
         </is>
       </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>STORY-20.10</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -15848,6 +16912,11 @@
           <t>src/research/hypotheses/__init__.py; src/research/exit_grid.py; src/research/path/ambiguity_census.py; src/research/registry.py; src/utils/console_safe.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>STORY-36.22</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -15942,6 +17011,11 @@
           <t>src/config_layer/production_config.py; src/config_layer/config_builder.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>STORY-15.2</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -15989,6 +17063,11 @@
           <t>src/research/conditional_entropy_grid.py; src/research/contracts.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/qualification.py; src/utils/console_safe.py; src/runt</t>
         </is>
       </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -16036,6 +17115,11 @@
           <t>src/research/hypotheses/__init__.py; src/research/config.py; src/research/contracts.py; src/research/costs.py; src/research/exit_grid.py; src/research/forensics.py; src/research/indicators.py; src/res</t>
         </is>
       </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>STORY-41.67</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -16083,6 +17167,11 @@
           <t>src/research/adapters/structural_event_source.py; src/research/conditional_entropy_grid.py; src/research/structural_asymmetry.py; src/utils/console_safe.py; src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>STORY-36.20</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -16130,6 +17219,11 @@
           <t xml:space="preserve">src/research/contracts.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/selection_effect.py; src/runtime/backtest_v2.py; scripts/research/execution_planner_replay.py; </t>
         </is>
       </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>STORY-30.3</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -16224,6 +17318,11 @@
           <t>src/research/config.py; src/research/cross_sectional.py; src/research/provenance.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>STORY-36.28</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -16271,6 +17370,11 @@
           <t>src/research/config.py; src/research/cross_sectional.py; src/research/provenance.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>STORY-36.19</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -16318,6 +17422,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/config.py; src/research/costs.py; src/research/measurement/metrics.py; src/research/provenance.py; src/research/qua</t>
         </is>
       </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>STORY-25.13</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -16365,6 +17474,11 @@
           <t>src/research/config.py; src/research/cross_sectional.py; src/research/provenance.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>STORY-36.28</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -16412,6 +17526,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/config.py; src/research/costs.py; src/research/measurement/metrics.py; src/research/provenance.py; src/research/qua</t>
         </is>
       </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>STORY-36.21</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -16459,6 +17578,11 @@
           <t xml:space="preserve">src/research/controls/__init__.py; src/research/config.py; src/research/costs.py; src/research/measurement/metrics.py; src/research/qualification.py; src/research/registry.py; src/research/runner.py; </t>
         </is>
       </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>STORY-28.1</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -16506,6 +17630,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/candle_state/__init__.py; src/research/candle_state/reporting.py; src/research/config.py; src/research/costs.py; sr</t>
         </is>
       </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -16553,6 +17682,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/config.py; src/research/costs.py; src/research/measurement/metrics.py; src/research/provenance.py; src/research/qua</t>
         </is>
       </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>STORY-30.3; STORY-34.2; STORY-36.14; STORY-36.17; STORY-36.19; STORY-36.21</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -16600,6 +17734,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/interpreters/regime_observer.py; src/research/config.py; src/research/costs.py; src/research/process_characterization.py; sr</t>
         </is>
       </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>STORY-34.1; STORY-34.2</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -16647,6 +17786,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/interpreters/regime_observer.py; src/research/config.py; src/research/costs.py; src/research/process_characterization.py; sr</t>
         </is>
       </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>STORY-34.1</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -16694,6 +17838,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/data_ingestion/xauusd_phase1_candidate.py; src/research/config.py; src/research/costs.py; src/research/measurement/metrics.p</t>
         </is>
       </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -16741,6 +17890,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/candle_state/__init__.py; src/research/candle_state/reporting.py; src/research/config.py; src/research/costs.py; sr</t>
         </is>
       </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -16788,6 +17942,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/data_ingestion/session_autoderive.py; src/research/candle_state/encoder.py; src/research/config.py; src/research/costs.py; s</t>
         </is>
       </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>STORY-41.65</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -16835,6 +17994,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/data_ingestion/xauusd_phase1_candidate.py; src/research/config.py; src/research/costs.py; src/research/measurement/metrics.p</t>
         </is>
       </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -16882,6 +18046,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py; src/config_layer/goal_validator.py; src/research/adapters/spi</t>
         </is>
       </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>STORY-37.7</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -16929,6 +18098,11 @@
           <t>src/research/xau_metals_protocol.py</t>
         </is>
       </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -16976,6 +18150,11 @@
           <t>src/config_layer/rr/rr_pattern_miner.py; scripts/governance/rr_l1_freeze_certificate.py</t>
         </is>
       </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>STORY-25.37</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -17023,6 +18202,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; scripts/governance/rr_l1_freeze_certificate.py</t>
         </is>
       </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>STORY-25.37</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -17070,6 +18254,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/research/contracts.py; src/research/measurement/forward_walk.py; src/research/zone_label_audit.py; scripts/research/zone_label_audit.py; scripts/governance/rr_l1</t>
         </is>
       </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>STORY-25.37</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -17117,6 +18306,11 @@
           <t>scripts/governance/rr_l1_freeze_certificate.py</t>
         </is>
       </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>STORY-25.37</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -17164,6 +18358,11 @@
           <t>src/config_layer/rr/rr_pattern_miner.py; src/features/feature_schema.py; src/engines/heuristic_gaussian_engine.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>STORY-25.37</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -17211,6 +18410,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/crt_state_resolver.py; src/features/feature_states.py; src/features/registry/__init__.py; src/config_layer/production_con</t>
         </is>
       </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>STORY-20.6; STORY-20.11; STORY-20.20</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -17305,6 +18509,11 @@
           <t>src/research/evidence/__main__.py</t>
         </is>
       </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -17352,6 +18561,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/data_ingestion/xauusd_phase1_candidate.py; src/research/adapters/spine_signal_source.py; src/research/config.py; src/researc</t>
         </is>
       </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>STORY-54.1</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -17399,6 +18613,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/msip/interpretation_config.py; src/msip/shadow_emitter.p</t>
         </is>
       </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>STORY-51.3</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -17442,6 +18661,11 @@
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr"/>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>STORY-51.3</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -17489,6 +18713,11 @@
           <t>src/research/model_runners/contracts.py; src/research/model_runners/runner.py</t>
         </is>
       </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -17536,6 +18765,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/data_ingestion/xauusd_phase1_candidate.py; src/research/contracts.py; src/research/mea</t>
         </is>
       </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -17583,6 +18817,11 @@
           <t>src/research/model_runners/runner.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py</t>
         </is>
       </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -17630,6 +18869,11 @@
           <t>src/research/shape_statistics.py</t>
         </is>
       </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -17724,6 +18968,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/features/parent_candle.py; src/features/smc/_geometry.py; src/features/smc/breaker.py; src/features/smc/fvg.py; src/featur</t>
         </is>
       </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>STORY-25.27</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -17771,6 +19020,11 @@
           <t>src/research/synthetic/ontology.py; src/research/synthetic/story_builder.py; src/research/synthetic/story_registry.py; src/utils/run_manifest.py</t>
         </is>
       </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -17818,6 +19072,11 @@
           <t>src/features/feature_schema.py; src/utils/console_safe.py; src/utils/run_manifest.py</t>
         </is>
       </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -17865,6 +19124,11 @@
           <t>src/replay/replay_similarity_index.py; src/utils/console_safe.py; src/utils/run_manifest.py</t>
         </is>
       </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -17912,6 +19176,11 @@
           <t>src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>STORY-41.66</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -17959,6 +19228,11 @@
           <t>src/bitnet/zone_cosine_searcher.py; src/engines/live_engine.py; src/engines/zone_gate_engine.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -18006,6 +19280,11 @@
           <t>src/research/envelope_offline/train.py</t>
         </is>
       </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -18053,6 +19332,11 @@
           <t>src/research/candle_state/encoder.py; src/research/candle_state/info_robustness.py; src/research/candle_state/mtf_conjunction.py; src/research/candle_state/transition_target.py; src/utils/console_safe</t>
         </is>
       </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -18096,6 +19380,11 @@
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr"/>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>STORY-20.12; STORY-25.12; STORY-31.13</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -18143,6 +19432,11 @@
           <t>src/features/crt_state_resolver.py; src/utils/console_safe.py; src/features/feature_schema.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>STORY-20.6</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -18190,6 +19484,11 @@
           <t>src/research/band_validation.py; src/research/shape_statistics.py</t>
         </is>
       </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>STORY-25.36</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -18237,6 +19536,11 @@
           <t>src/research/oracle/scan.py</t>
         </is>
       </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -18284,6 +19588,11 @@
           <t>src/research/visual_crt/measure.py</t>
         </is>
       </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -18331,6 +19640,11 @@
           <t>src/research/resample.py; src/utils/console_safe.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -18374,6 +19688,11 @@
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr"/>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -18421,6 +19740,11 @@
           <t>scripts/research/visual_state_questions.py</t>
         </is>
       </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>STORY-20.12</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -18468,6 +19792,11 @@
           <t>scripts/research/crt_state_confusion_matrix.py; scripts/research/visual_state_questions.py</t>
         </is>
       </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>STORY-20.12</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -18515,6 +19844,11 @@
           <t>src/research/episode_agreement.py; src/research/episode_propositions.py</t>
         </is>
       </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -18562,6 +19896,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/engines/crt_engine.py; src/engines/heuristic_gaussian_engine.py; src/engines/rr_engine.py; src/engines/zone_cluster_score.</t>
         </is>
       </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -18609,6 +19948,11 @@
           <t>src/data_ingestion/xauusd_phase1_candidate.py; src/research/contracts.py; src/research/measurement/forward_walk.py; src/research/costs.py</t>
         </is>
       </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -18656,6 +20000,11 @@
           <t>src/data_ingestion/xauusd_phase1_candidate.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/gaussian_schema_contract.py; src/training/trainer.py</t>
         </is>
       </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -18703,6 +20052,11 @@
           <t>src/research/qualification.py; src/research/contracts.py; src/research/costs.py; src/research/measurement/metrics.py</t>
         </is>
       </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -18750,6 +20104,11 @@
           <t>src/research/mt5_cost_calibration.py; mt5_analytics/core/mt5_adapter.py</t>
         </is>
       </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>STORY-38.1</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -18793,6 +20152,11 @@
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr"/>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>STORY-38.1</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -18840,6 +20204,11 @@
           <t>src/research/xau_metals_protocol.py; src/data_ingestion/xauusd_phase1_candidate.py; src/research/contracts.py; src/research/measurement/forward_walk.py</t>
         </is>
       </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>STORY-38.1</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -18883,6 +20252,11 @@
         </is>
       </c>
       <c r="I369" s="2" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -18930,6 +20304,11 @@
           <t>src/features/feature_schema.py; src/research/__init__.py; src/research/zone_label_audit.py</t>
         </is>
       </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>STORY-37.3</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -18973,6 +20352,11 @@
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr"/>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -19082,6 +20466,11 @@
           <t>src/config_layer/market_router.py; src/config_layer/config_builder.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>STORY-6.3; STORY-18.1; STORY-18.10; STORY-18.12; STORY-33.20</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -19121,6 +20510,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/llm_scorer.py; src/runtime/backtest_v2.py; src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -19160,6 +20554,11 @@
           <t>src/utils/console_safe.py; src/config_layer/crt_engine_v2.py; src/config_layer/config_builder.py; src/config_layer/llm_scorer.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>STORY-6.3; STORY-14.2; STORY-18.1; STORY-18.12; STORY-23.8; STORY-33.16; STORY-33.20; STORY-35.2; STORY-41.4</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -19199,6 +20598,11 @@
           <t>src/training/stage1_dataset_builder.py</t>
         </is>
       </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -19238,6 +20642,11 @@
           <t>src/features/feature_schema.py; src/features/dataset_builder.py; src/training/trainer.py; src/training/evaluator.py; src/core/model_registry.py; src/config_layer/production_config.py; src/features/fea</t>
         </is>
       </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-18.10; STORY-18.11; STORY-18.12; STORY-19.7; STORY-30.6; STORY-33.20; STORY-35.2; STORY-37.7; STORY-37.10; STORY-37.12; STORY-38.2; STORY-38.3; STORY-38.4</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -19312,6 +20721,11 @@
           <t>src/features/feature_pipeline.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-16.1; STORY-16.4; STORY-18.12; STORY-33.20</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -19429,6 +20843,11 @@
           <t>src/training/train_pipeline.py; src/training/trainer.py</t>
         </is>
       </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-33.20; STORY-37.11; STORY-38.5; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -19468,6 +20887,11 @@
           <t>src/config_layer/rr/rr_dataset_builder.py; src/config_layer/rr/rr_pattern_miner.py; src/core/model_registry.py</t>
         </is>
       </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-16.4; STORY-18.11; STORY-18.12; STORY-35.2; STORY-37.13</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -19507,6 +20931,11 @@
           <t>src/features/feature_schema.py; src/features/dataset_builder.py; config_layer.production_loader; src/utils/integrity_events.py; src/core/model_registry.py</t>
         </is>
       </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-25.23; STORY-37.12; STORY-38.2</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -19542,6 +20971,11 @@
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-32.2; STORY-34.3; STORY-37.7; STORY-41.4</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -19581,6 +21015,11 @@
           <t>src/core/types.py; src/core/feature_store.py; src/features/feature_schema.py; src/scanner/spine_adapter.py; src/core/fusion_engine.py; src/core/engine_runner.py; src/core/signal_audit.py; src/core/acc</t>
         </is>
       </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -19628,6 +21067,11 @@
           <t>src/agent/__init__.py; src/agent/agent_core.py; src/agent/grok_agentic.py; src/agent/state.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.5; STORY-14.6; STORY-14.8; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -19675,6 +21119,11 @@
           <t>src/agent/tool_planner.py; src/config_layer/llm_inference_client.py</t>
         </is>
       </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.4; STORY-14.8; STORY-31.24; STORY-33.5; STORY-33.17</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -19722,6 +21171,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.4; STORY-14.8; STORY-18.12; STORY-29.6; STORY-33.5</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -19769,6 +21223,11 @@
           <t>src/config_layer/state_identity.py; src/runtime/backtest_v2.py; src/config_layer/production_config.py; src/config_layer/goal_schema.py; src/config_layer/goal_validator.py</t>
         </is>
       </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.8; STORY-18.1; STORY-18.12; STORY-20.29; STORY-21.3; STORY-23.8; STORY-31.20; STORY-33.17; STORY-33.18; STORY-33.20; STORY-35.2; STORY-37.12; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -19816,6 +21275,11 @@
           <t>src/bitnet/bitnet_inference.py; src/features/feature_schema.py; src/features/schema_validator.py; src/features/__init__.py; src/features/fm_resolve.py; src/config_layer/state_identity.py; src/config_l</t>
         </is>
       </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-15.2; STORY-16.3; STORY-16.5; STORY-18.8; STORY-18.11; STORY-18.13; STORY-20.1; STORY-20.4; STORY-20.6; STORY-20.14; STORY-20.17; STORY-20.22; STORY-20.26; STORY-20.29; STORY-20.30; STORY-21.1; STORY-21.2; STORY-23.4; STORY-23.8; STORY-25.6; STORY-25.9; STORY-25.12; STORY-25.18; STORY-25.19; STORY-25.29; STORY-27.1; STORY-29.2; STORY-31.1; STORY-31.5; STORY-31.6; STORY-31.12; STORY-31.16; STORY-31.19; STORY-31.20; STORY-31.21; STORY-33.15; STORY-33.16; STORY-36.2; STORY-36.3; STORY-36.5; STORY-36.14; STORY-36.21; STORY-36.23; STORY-41.11; STORY-41.33; STORY-41.38; STORY-41.46; STORY-41.52</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -19863,6 +21327,11 @@
           <t>src/config_layer/production_config.py; src/engines/scoring_engine.py; src/features/__init__.py</t>
         </is>
       </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>STORY-20.5; STORY-37.12</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -19910,6 +21379,11 @@
           <t>src/utils/logging_config.py; src/core/gate_intelligence.py</t>
         </is>
       </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-14.2; STORY-14.8; STORY-16.2; STORY-18.1; STORY-18.12; STORY-20.5; STORY-20.16; STORY-23.1; STORY-23.2; STORY-23.4; STORY-23.6; STORY-25.17; STORY-29.2; STORY-31.10; STORY-31.20; STORY-31.23</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -19957,6 +21431,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>STORY-20.5; STORY-27.1; STORY-27.2</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -20004,6 +21483,11 @@
           <t>src/config_layer/goal_schema.py</t>
         </is>
       </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>STORY-27.1; STORY-27.2; STORY-31.7</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -20051,6 +21535,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>STORY-18.5; STORY-18.8; STORY-20.4; STORY-20.16; STORY-20.27; STORY-20.28; STORY-31.5; STORY-31.12; STORY-31.19; STORY-31.20; STORY-31.21; STORY-36.2; STORY-36.12; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -20098,6 +21587,11 @@
           <t>src/control_plane/cp_types.py</t>
         </is>
       </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>STORY-6.2; STORY-14.2; STORY-14.4; STORY-14.8; STORY-18.1; STORY-18.12; STORY-19.3; STORY-19.5; STORY-19.6; STORY-21.2; STORY-23.4; STORY-25.12; STORY-33.5; STORY-35.2; STORY-36.13; STORY-41.8; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -20145,6 +21639,11 @@
           <t>src/control_plane/jobs.py; src/control_plane/registry.py; src/control_plane/dashboard_api.py; src/control_plane/report_api.py; src/control_plane/context_report.py; src/control_plane/code_context_extra</t>
         </is>
       </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>STORY-6.2; STORY-7.1; STORY-14.2; STORY-14.8; STORY-18.1; STORY-18.12; STORY-19.1; STORY-19.2; STORY-19.3; STORY-19.4; STORY-19.5; STORY-19.7; STORY-20.11; STORY-25.31; STORY-42.1; STORY-42.3; STORY-42.7</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -20192,6 +21691,11 @@
           <t>src/core/dynamic_threshold.py</t>
         </is>
       </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-14.8; STORY-18.1; STORY-18.2; STORY-23.1; STORY-23.4; STORY-25.17; STORY-26.1; STORY-31.3; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -20239,6 +21743,11 @@
           <t>src/engines/trap_validator_engine.py; src/engines/crt_engine.py; src/engines/heuristic_gaussian_engine.py; src/engines/ml_gaussian_engine.py; src/engines/zone_gate_engine.py; src/engines/zone_cluster_</t>
         </is>
       </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>STORY-1.2; STORY-1.4; STORY-2.3; STORY-2.4; STORY-3.2; STORY-5.4; STORY-8.2; STORY-8.3; STORY-10.3; STORY-14.2; STORY-14.3; STORY-14.8; STORY-16.2; STORY-18.1; STORY-18.2; STORY-18.8; STORY-18.10; STORY-18.11; STORY-19.2; STORY-20.1; STORY-20.5; STORY-20.16; STORY-21.2; STORY-23.1; STORY-23.6; STORY-25.17; STORY-25.21; STORY-25.28; STORY-31.1; STORY-31.3; STORY-31.10; STORY-31.12; STORY-31.20; STORY-31.22; STORY-32.1; STORY-33.1; STORY-33.5; STORY-33.8; STORY-34.3; STORY-35.2; STORY-37.6; STORY-37.7; STORY-37.12; STORY-41.31; STORY-41.56; STORY-47.4</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -20286,6 +21795,11 @@
           <t>src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>STORY-1.3; STORY-2.5; STORY-3.2; STORY-14.8; STORY-18.1; STORY-18.14; STORY-20.1; STORY-20.5; STORY-20.16; STORY-23.1; STORY-23.4; STORY-25.17; STORY-26.1; STORY-31.10; STORY-31.20; STORY-31.25; STORY-34.3; STORY-37.7; STORY-37.12; STORY-38.2</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -20333,6 +21847,11 @@
           <t>src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>STORY-15.2; STORY-23.6; STORY-29.2; STORY-31.10; STORY-31.23</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -20380,6 +21899,11 @@
           <t>src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>STORY-2.1; STORY-3.2; STORY-14.8; STORY-18.1; STORY-18.12; STORY-20.5; STORY-21.3; STORY-23.1; STORY-23.2; STORY-23.4; STORY-23.6; STORY-25.12; STORY-29.2; STORY-31.3; STORY-31.19; STORY-31.20; STORY-41.56</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -20427,6 +21951,11 @@
           <t>src/engines/scoring_engine.py</t>
         </is>
       </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-18.11; STORY-20.30; STORY-23.1; STORY-31.12; STORY-31.19; STORY-31.20; STORY-33.11</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -20474,6 +22003,11 @@
           <t>src/features/feature_schema.py; src/utils/registry_refresh.py; src/config_layer/model_paths.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-18.11; STORY-23.1; STORY-25.17; STORY-31.19; STORY-37.7; STORY-37.10; STORY-37.12; STORY-38.3; STORY-41.33</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -20521,6 +22055,11 @@
           <t>src/core/model_registry.py; src/training/trainer.py; src/features/feature_schema.py; src/features/gaussian_schema_contract.py</t>
         </is>
       </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>STORY-1.4; STORY-3.2; STORY-18.1; STORY-18.11; STORY-20.7; STORY-23.1; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -20568,6 +22107,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1; STORY-31.19; STORY-37.1; STORY-37.12; STORY-41.33</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -20615,6 +22159,11 @@
           <t>src/features/feature_schema.py; src/config_layer/llm_scorer.py; src/features/schema_validator.py; src/features/fm_resolve.py; src/bitnet/zone_cosine_searcher.py</t>
         </is>
       </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>STORY-26.1; STORY-31.12; STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -20662,6 +22211,11 @@
           <t>src/features/feature_schema.py; src/utils/zone_schema_migrator.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-18.11; STORY-18.13; STORY-23.1; STORY-25.21; STORY-29.4; STORY-31.16; STORY-35.2; STORY-37.6; STORY-37.12; STORY-38.3; STORY-41.33</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -20709,6 +22263,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>STORY-29.2; STORY-33.1; STORY-33.4</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -20756,6 +22315,11 @@
           <t>src/features/feature_schema.py; src/features/schema_validator.py; src/features/feature_monitor.py; src/data_ingestion/ohlcv_schema.py; src/utils/logging_config.py; src/config_layer/production_config.p</t>
         </is>
       </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-14.2; STORY-14.8; STORY-18.1; STORY-18.3; STORY-20.20; STORY-20.29; STORY-23.1; STORY-23.4; STORY-25.3; STORY-25.6; STORY-25.21; STORY-25.23; STORY-25.29; STORY-25.30; STORY-25.33; STORY-29.2; STORY-29.4; STORY-31.1; STORY-31.19; STORY-31.20; STORY-31.22; STORY-33.7; STORY-35.2; STORY-36.5; STORY-36.22; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -20803,6 +22367,11 @@
           <t>src/features/session_classifier.py; src/features/schema_validator.py</t>
         </is>
       </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-16.4; STORY-18.13; STORY-20.7; STORY-20.20; STORY-20.26; STORY-23.4; STORY-25.4; STORY-25.6; STORY-25.12; STORY-25.17; STORY-25.18; STORY-25.20; STORY-25.28; STORY-25.29; STORY-25.32; STORY-29.2; STORY-31.16; STORY-31.19; STORY-31.20; STORY-31.21; STORY-33.5; STORY-35.2; STORY-36.5; STORY-36.12; STORY-37.2; STORY-37.12; STORY-38.2; STORY-38.6; STORY-47.1; STORY-48.2; STORY-48.3</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -20850,6 +22419,11 @@
           <t>src/config_layer/config_validator.py</t>
         </is>
       </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-6.3; STORY-10.3; STORY-14.2; STORY-14.5; STORY-14.8; STORY-14.10; STORY-18.1; STORY-18.7; STORY-18.10; STORY-18.12; STORY-18.14; STORY-20.29; STORY-20.30; STORY-21.1; STORY-23.1; STORY-23.4; STORY-23.8; STORY-27.2; STORY-31.20; STORY-33.3; STORY-33.9; STORY-33.14; STORY-33.16; STORY-33.17; STORY-33.18; STORY-33.19; STORY-33.20; STORY-35.2; STORY-37.12; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -20897,6 +22471,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>STORY-34.2; STORY-36.22</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -20944,6 +22523,11 @@
           <t>src/research/candle_state/encoder.py; src/research/contracts.py; src/research/indicators.py; src/research/registry.py</t>
         </is>
       </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -20991,6 +22575,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>STORY-27.2; STORY-36.1; STORY-36.17; STORY-36.21; STORY-41.39</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -21038,6 +22627,11 @@
           <t>src/features/feature_schema.py; src/data_ingestion/ohlcv_schema.py; src/data_ingestion/xauusd_phase1_candidate.py; src/data_ingestion/dataset_integrity.py; src/utils/console_safe.py; src/config_layer/</t>
         </is>
       </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-6.3; STORY-12.4; STORY-14.2; STORY-14.8; STORY-14.9; STORY-14.10; STORY-15.2; STORY-16.5; STORY-18.1; STORY-18.2; STORY-18.7; STORY-18.8; STORY-18.10; STORY-18.11; STORY-18.12; STORY-18.13; STORY-18.14; STORY-20.13; STORY-20.16; STORY-20.20; STORY-20.22; STORY-20.24; STORY-20.29; STORY-20.30; STORY-20.31; STORY-20.32; STORY-21.2; STORY-23.1; STORY-23.8; STORY-25.1; STORY-25.4; STORY-25.8; STORY-25.9; STORY-25.18; STORY-25.20; STORY-25.21; STORY-25.29; STORY-27.1; STORY-27.2; STORY-28.1; STORY-30.5; STORY-31.4; STORY-31.20; STORY-31.25; STORY-33.1; STORY-33.10; STORY-33.15; STORY-33.16; STORY-33.17; STORY-33.18; STORY-33.20; STORY-36.5; STORY-36.14; STORY-36.21; STORY-38.2; STORY-38.3; STORY-41.11; STORY-41.31; STORY-41.38; STORY-41.50; STORY-41.55; STORY-41.56; STORY-41.59</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -21083,6 +22677,11 @@
       <c r="I419" s="2" t="inlineStr">
         <is>
           <t>src/core/collector.py; src/core/engine_runner.py; src/core/gate_intelligence.py; src/engines/live_engine.py; src/config_layer/execution_planner.py; src/config_layer/production_config.py; src/core/ultr</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.5; STORY-16.5; STORY-18.1; STORY-18.10; STORY-18.11; STORY-20.16; STORY-20.26; STORY-21.3; STORY-23.6; STORY-25.21; STORY-29.2; STORY-29.4; STORY-30.5; STORY-30.6; STORY-31.3; STORY-31.10; STORY-32.1; STORY-33.1; STORY-38.3; STORY-41.31; STORY-41.51</t>
         </is>
       </c>
     </row>
@@ -21171,6 +22770,11 @@
           <t>agent{modes}</t>
         </is>
       </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -21218,6 +22822,11 @@
           <t>src/agent/audit.py; src/agent/executor.py; src/agent/goal_loop.py; src/agent/grok_agentic.py; src/agent/intent_router.py; src/agent/plan_compiler.py; src/agent/state.py; src/agent/tool_planner.py; src</t>
         </is>
       </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.9; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -21265,6 +22874,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.10; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -21312,6 +22926,11 @@
           <t>src/agent/tool_registry.py; src/agent/state.py</t>
         </is>
       </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -21359,6 +22978,11 @@
           <t>src/agent/groq_client.py; src/config_layer/production_config.py; src/control_plane/registry.py</t>
         </is>
       </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.10; STORY-18.12; STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -21406,6 +23030,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -21500,6 +23129,11 @@
           <t>src/agent/goal.py</t>
         </is>
       </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -21547,6 +23181,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-18.12; STORY-25.31</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -21594,6 +23233,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-14.10</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -21688,6 +23332,11 @@
           <t>src/agent/tool_registry.py; src/core/engine_runner.py; src/config_layer/production_config.py; src/core/fusion_engine.py; src/config_layer/execution_planner.py; src/core/ultron_risk_gate.py; src/config</t>
         </is>
       </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -21735,6 +23384,11 @@
           <t>src/agent/tool_registry.py; src/agent/findings_synthesizer.py</t>
         </is>
       </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -21782,6 +23436,11 @@
           <t>src/agent/tool_registry.py; src/governance/reflection_buffer_advanced.py; src/governance/bitnet_governance_executor.py; src/governance/shadow_promotion_gate.py; src/governance/orchestrator.py</t>
         </is>
       </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.8</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -21829,6 +23488,11 @@
           <t>src/agent/tool_registry.py; agent{log_query}</t>
         </is>
       </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -21923,6 +23587,11 @@
           <t>src/agent/tool_registry.py; src/config_layer/crt_engine_v2.py; src/config_layer/production_config.py; src/engines/live_engine.py; src/inout/live_rail/types.py; src/runtime/live_engine_hook.py; src/run</t>
         </is>
       </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-21.3; STORY-25.12; STORY-29.2; STORY-31.16</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -21970,6 +23639,11 @@
           <t>src/agent/tool_registry.py; src/governance/semantic_grounding.py</t>
         </is>
       </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>STORY-14.3; STORY-25.12; STORY-33.5</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -22064,6 +23738,11 @@
           <t>src/agent/plan_compiler.py</t>
         </is>
       </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -22205,6 +23884,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>STORY-14.2</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -22252,6 +23936,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.9</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -22297,6 +23986,11 @@
       <c r="I445" s="2" t="inlineStr">
         <is>
           <t>(none / stdlib-only)</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.4; STORY-14.8; STORY-18.12; STORY-19.3; STORY-19.8; STORY-29.6; STORY-33.5; STORY-36.5; STORY-41.31; STORY-41.36; STORY-41.52; STORY-44.3</t>
         </is>
       </c>
     </row>
@@ -22377,6 +24071,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>STORY-15.1</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -22416,6 +24115,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>STORY-20.29; STORY-25.23; STORY-31.7; STORY-31.11; STORY-36.8; STORY-36.9</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -22455,6 +24159,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>STORY-20.29</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -22494,6 +24203,11 @@
           <t>src/analytics/__init__.py; src/data_ingestion/ohlcv_schema.py; src/runtime/backtest_v2.py; src/config_layer/production_config.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>STORY-15.2; STORY-18.12; STORY-20.29; STORY-21.3; STORY-25.21</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -22572,6 +24286,11 @@
           <t>src/bitnet/zone_validator.py; src/bitnet/zone_cosine_searcher.py; src/bitnet/stability_checker.py; src/engines/scoring_engine.py</t>
         </is>
       </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-37.6</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -22689,6 +24408,11 @@
           <t>src/bitnet/model_contract.py; src/features/feature_schema.py; src/utils/integrity_events.py; src/bitnet/composition.py</t>
         </is>
       </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-14.8; STORY-16.1; STORY-16.3; STORY-18.1; STORY-23.1; STORY-25.32; STORY-46.1</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -22728,6 +24452,11 @@
           <t>src/config_layer/model_paths.py</t>
         </is>
       </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>STORY-25.16; STORY-25.26</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -22767,6 +24496,11 @@
           <t>src/bitnet/bitnet_inference.py; src/bitnet/model_contract.py; src/features/feature_schema.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-16.1; STORY-16.5; STORY-25.32; STORY-37.12</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -22884,6 +24618,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>STORY-25.17</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -22962,6 +24701,11 @@
           <t>src/bitnet/zone_cosine_searcher.py</t>
         </is>
       </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>STORY-36.5</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -23157,6 +24901,11 @@
           <t>src/features/feature_schema.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>STORY-16.1; STORY-16.5; STORY-25.32; STORY-38.2</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -23235,6 +24984,11 @@
           <t>src/bitnet/contract_c_trainer.py; src/bitnet/label_contracts.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>STORY-16.1</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -23313,6 +25067,11 @@
           <t>src/bitnet/zone_cosine_searcher.py</t>
         </is>
       </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>STORY-36.5</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -23352,6 +25111,11 @@
           <t>src/features/dataset_builder.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>STORY-37.3</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -23469,6 +25233,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/features/calendar_periods.py; src/research/resample.py; src/runtime/backtest_v2.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>STORY-20.11; STORY-41.32; STORY-42.4; STORY-42.8</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -23508,6 +25277,11 @@
           <t>src/charts/chart_series.py; src/config_layer/production_config.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>STORY-20.10; STORY-20.11</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -23547,6 +25321,11 @@
           <t>src/charts/chart_series.py</t>
         </is>
       </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>STORY-41.32</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -23586,6 +25365,11 @@
           <t>src/cognitive/cognitive_bus.py</t>
         </is>
       </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -23625,6 +25409,11 @@
           <t>src/utils/logging_config.py; src/replay/replay_memory_engine.py; src/regime/market_state_cluster_engine.py; src/engines/tradenet_meta_engine.py; src/core/hierarchical_meta_fusion.py; src/events/event_</t>
         </is>
       </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-21.2; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -23703,6 +25492,11 @@
           <t>src/config_layer/state_identity.py; src/config_layer/market_router.py; src/config_layer/crt_config_provenance.py</t>
         </is>
       </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-18.9; STORY-18.12; STORY-20.5; STORY-20.32</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -23742,6 +25536,11 @@
           <t>src/config_layer/state_identity.py; src/config_layer/config_builder.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>STORY-33.10</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -23781,6 +25580,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>STORY-25.5</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -23820,6 +25624,11 @@
           <t>src/config_layer/state_identity.py; src/config_layer/crt_engine_v2.py; src/config_layer/parent_crt.py</t>
         </is>
       </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>STORY-20.4; STORY-20.18; STORY-31.5; STORY-31.6; STORY-31.20; STORY-31.21</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -23859,6 +25668,11 @@
           <t>src/config_layer/llm_narrative.py</t>
         </is>
       </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -23898,6 +25712,11 @@
           <t>src/config_layer/production_config.py; src/config_layer/llm_scorer.py; src/config_layer/llm_narrative.py</t>
         </is>
       </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>STORY-1.1; STORY-14.10; STORY-18.12; STORY-20.24; STORY-21.3</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -23976,6 +25795,11 @@
           <t>src/config_layer/llm_inference_client.py</t>
         </is>
       </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-20.5; STORY-25.28</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -24015,6 +25839,11 @@
           <t>src/config_layer/state_identity.py</t>
         </is>
       </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -24054,6 +25883,11 @@
           <t>src/config_layer/state_identity.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>STORY-25.20; STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -24132,6 +25966,11 @@
           <t>src/config_layer/model_paths.py</t>
         </is>
       </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>STORY-18.8</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -24171,6 +26010,11 @@
           <t>src/config_layer/state_identity.py; src/structure/predicates.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>STORY-20.4; STORY-20.10; STORY-20.25; STORY-20.33; STORY-25.12; STORY-31.5; STORY-31.6; STORY-31.20; STORY-36.2; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -24210,6 +26054,11 @@
           <t>src/config_layer/model_resolver.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>STORY-18.7; STORY-18.8</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -24249,6 +26098,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/state_identity.py; src/config_layer/crt_config_provenance.py</t>
         </is>
       </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>STORY-2.1; STORY-2.5; STORY-14.8; STORY-14.9; STORY-16.5; STORY-18.1; STORY-18.2; STORY-18.9; STORY-18.10; STORY-18.11; STORY-18.12; STORY-18.13; STORY-18.14; STORY-20.5; STORY-20.32; STORY-23.8; STORY-27.2; STORY-29.5; STORY-31.20; STORY-32.2; STORY-33.14; STORY-33.18</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -24327,6 +26181,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/schema_validator.py</t>
         </is>
       </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-25.21; STORY-37.13; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -24366,6 +26225,11 @@
           <t>src/config_layer/rr/rr_pattern_miner.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/schema_validator.py; src/config_layer/production_config.py; src/utils/integrity_</t>
         </is>
       </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>STORY-1.3; STORY-14.9; STORY-16.2; STORY-18.1; STORY-18.11; STORY-20.5; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -24405,6 +26269,11 @@
           <t>src/features/feature_schema.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>STORY-18.11; STORY-20.5; STORY-35.2; STORY-37.1; STORY-37.13</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -24444,6 +26313,11 @@
           <t>src/config_layer/production_bundle.py; src/config_layer/production_config.py; src/features/registry/__init__.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>STORY-18.7; STORY-18.8</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -24483,6 +26357,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>STORY-18.5; STORY-25.19; STORY-31.5</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -24522,6 +26401,11 @@
           <t>src/config_layer/state_identity.py; src/config_layer/state_contract.py; src/features/fm_resolve.py</t>
         </is>
       </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>STORY-18.5; STORY-18.8; STORY-25.19; STORY-31.2; STORY-31.5; STORY-36.2; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -24561,6 +26445,11 @@
           <t>src/config_layer/state_identity.py</t>
         </is>
       </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>STORY-31.5; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -24639,6 +26528,11 @@
           <t>ast</t>
         </is>
       </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>STORY-19.2; STORY-19.6; STORY-19.7</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -24678,6 +26572,11 @@
           <t>anthropic</t>
         </is>
       </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>STORY-19.2; STORY-19.3; STORY-19.6; STORY-19.7; STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -24717,6 +26616,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -24756,6 +26660,11 @@
           <t>src/agent/groq_client.py</t>
         </is>
       </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>STORY-25.31; STORY-41.12; STORY-41.20; STORY-42.1; STORY-42.2; STORY-42.6</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -24795,6 +26704,11 @@
           <t>ast</t>
         </is>
       </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>STORY-19.2</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -24834,6 +26748,11 @@
           <t>src/control_plane/monitors.py; src/control_plane/registry.py; src/control_plane/cp_types.py</t>
         </is>
       </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -24990,6 +26909,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>STORY-18.2</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -25029,6 +26953,11 @@
           <t>src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>STORY-21.3</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -25068,6 +26997,11 @@
           <t>src/utils/logging_config.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-14.10; STORY-18.1; STORY-18.10; STORY-18.11; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -25107,6 +27041,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>STORY-18.2; STORY-20.5</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -25146,6 +27085,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>STORY-18.2</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -25185,6 +27129,11 @@
           <t>src/features/feature_schema.py; src/features/schema_validator.py; src/features/feature_pipeline.py; src/features/causal_structure.py</t>
         </is>
       </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>STORY-18.3; STORY-23.6; STORY-25.21; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -25263,6 +27212,11 @@
           <t>src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -25302,6 +27256,11 @@
           <t>src/training/evaluator.py; src/features/feature_schema.py; src/config_layer/production_config.py; src/utils/integrity_events.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>STORY-2.6; STORY-18.1; STORY-26.1; STORY-35.2; STORY-37.2; STORY-37.3; STORY-37.10; STORY-37.13; STORY-38.2; STORY-38.3; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -25341,6 +27300,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>STORY-18.2; STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -25380,6 +27344,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>STORY-14.10</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -25419,6 +27388,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>STORY-18.11</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -25497,6 +27471,11 @@
           <t>src/core/ultron_risk_gate.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -25536,6 +27515,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>STORY-23.6; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -25614,6 +27598,11 @@
           <t>src/data_ingestion/ohlcv_schema.py; src/features/broker_clock.py</t>
         </is>
       </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-25.25</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -25653,6 +27642,11 @@
           <t>src/data_ingestion/ohlcv_schema.py</t>
         </is>
       </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>STORY-25.25; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -25692,6 +27686,11 @@
           <t>src/data_ingestion/ohlcv_schema.py; src/utils/console_safe.py; src/utils/logging_config.py; src/config_layer/production_config.py; src/data_ingestion/session_autoderive.py; src/features/feature_schema</t>
         </is>
       </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>STORY-25.8; STORY-25.9; STORY-25.13; STORY-25.18; STORY-27.2; STORY-30.4; STORY-31.20; STORY-41.4</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -25731,6 +27730,11 @@
           <t>src/config_layer/production_config.py; src/data_ingestion/ohlcv_schema.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-21.2; STORY-25.13; STORY-25.21; STORY-32.2</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -25770,6 +27774,11 @@
           <t>src/data_ingestion/clock_registry.py</t>
         </is>
       </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>STORY-25.13; STORY-25.18; STORY-25.21; STORY-25.25; STORY-27.2; STORY-29.2; STORY-30.4; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -25848,6 +27857,11 @@
           <t>src/data_ingestion/ohlcv_schema.py</t>
         </is>
       </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-25.8; STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -25942,6 +27956,11 @@
           <t>src/engines/heuristic_gaussian_engine.py</t>
         </is>
       </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -25989,6 +28008,11 @@
           <t>src/config_layer/model_paths.py; src/utils/registry_refresh.py; src/features/feature_schema.py; src/training/training_trigger.py; src/utils/integrity_events.py; src/features/dataset_builder.py; src/bi</t>
         </is>
       </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-14.10; STORY-18.12; STORY-20.5; STORY-23.1; STORY-25.12; STORY-25.16; STORY-25.26; STORY-29.2; STORY-30.6; STORY-31.25; STORY-37.6; STORY-37.8; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -26036,6 +28060,11 @@
           <t>src/config_layer/llm_scorer.py</t>
         </is>
       </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -26083,6 +28112,11 @@
           <t>src/utils/logging_config.py; src/core/model_registry.py; src/training/trainer.py; src/features/dataset_builder.py</t>
         </is>
       </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>STORY-33.1; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -26175,6 +28209,11 @@
       <c r="I543" s="2" t="inlineStr">
         <is>
           <t>src/engines/zone_gate_engine.py</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
         </is>
       </c>
     </row>
@@ -26216,6 +28255,11 @@
           <t>src/events/event_fabric.py</t>
         </is>
       </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -26255,6 +28299,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.4; STORY-21.1; STORY-21.2; STORY-21.3; STORY-25.6; STORY-33.13; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -26372,6 +28421,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>STORY-31.21</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -26411,6 +28465,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -26567,6 +28626,11 @@
           <t>src/expansion/policy_schema.py; src/expansion/config_mutator.py; src/expansion/evaluator.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-21.3</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -26739,6 +28803,11 @@
           <t>zoneinfo</t>
         </is>
       </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -26786,6 +28855,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>STORY-25.9; STORY-25.12; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -26833,6 +28907,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>STORY-25.22; STORY-31.1; STORY-31.20; STORY-36.2; STORY-36.23; STORY-41.41</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -26880,6 +28959,11 @@
           <t>src/features/fm_resolve.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>STORY-18.3</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -26927,6 +29011,11 @@
           <t>src/features/feature_schema.py; src/features/__init__.py; src/features/fm_resolve.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>STORY-14.9; STORY-25.21; STORY-25.32; STORY-31.1; STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -26974,6 +29063,11 @@
           <t>src/features/feature_schema.py; src/features/feature_states.py; src/features/registry/__init__.py; src/structure/predicates.py</t>
         </is>
       </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>STORY-20.4; STORY-20.6; STORY-20.14; STORY-20.20; STORY-20.26; STORY-20.27; STORY-25.17; STORY-31.2; STORY-31.5; STORY-33.9; STORY-36.2; STORY-36.6; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -27021,6 +29115,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>STORY-37.12; STORY-38.2</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -27068,6 +29167,11 @@
           <t>src/features/feature_schema.py; src/features/feature_builder.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>STORY-30.4; STORY-38.5</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -27115,6 +29219,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>STORY-25.22; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -27162,6 +29271,11 @@
           <t>src/features/dataset_builder.py</t>
         </is>
       </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>STORY-25.5</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -27256,6 +29370,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>STORY-8.3; STORY-18.1; STORY-18.12; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -27303,6 +29422,11 @@
           <t>src/features/registry/__init__.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>STORY-20.6; STORY-20.20; STORY-25.6; STORY-25.17; STORY-25.26; STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -27350,6 +29474,11 @@
           <t>src/features/registry/__init__.py; src/features/__init__.py</t>
         </is>
       </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>STORY-25.19</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -27397,6 +29526,11 @@
           <t>src/features/registry/__init__.py</t>
         </is>
       </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>STORY-31.1; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -27444,6 +29578,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>STORY-25.17</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -27491,6 +29630,11 @@
           <t>src/features/feature_states.py; src/features/registry/__init__.py</t>
         </is>
       </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>STORY-25.16; STORY-25.26</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -27538,6 +29682,11 @@
           <t>src/features/feature_states.py; src/features/registry/__init__.py</t>
         </is>
       </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>STORY-20.6; STORY-25.4; STORY-25.26; STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -27632,6 +29781,11 @@
           <t>src/features/feature_states.py; src/features/market_context.py</t>
         </is>
       </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>STORY-20.6; STORY-25.20; STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -27679,6 +29833,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>STORY-18.8; STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -27726,6 +29885,11 @@
           <t>src/features/calendar_periods.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-25.27; STORY-31.6; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -27773,6 +29937,11 @@
           <t>src/features/registry/_loader.py; src/features/registry/primitive_registry.py; src/features/registry/composition_registry.py; src/features/registry/derived_registry.py</t>
         </is>
       </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>STORY-20.27; STORY-25.5; STORY-25.12; STORY-25.15; STORY-25.22; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -27820,6 +29989,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>STORY-31.5</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -27961,6 +30135,11 @@
           <t>src/features/registry/_loader.py</t>
         </is>
       </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -28196,6 +30375,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>STORY-25.4</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -28243,6 +30427,11 @@
           <t>src/features/smc/_geometry.py; src/features/smc/order_block.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>STORY-25.27</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
@@ -28290,6 +30479,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>STORY-20.14; STORY-20.33; STORY-20.34</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
@@ -28337,6 +30531,11 @@
           <t>src/features/smc/_geometry.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>STORY-25.27</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -28431,6 +30630,11 @@
           <t>src/features/smc/_geometry.py; src/features/smc/order_block.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>STORY-25.27</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -28476,6 +30680,11 @@
       <c r="I594" s="2" t="inlineStr">
         <is>
           <t>src/features/smc/_geometry.py; src/config_layer/crt_engine_v2.py</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>STORY-25.27</t>
         </is>
       </c>
     </row>
@@ -28650,6 +30859,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>STORY-14.8</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -28697,6 +30911,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>STORY-30.4; STORY-32.1; STORY-33.1; STORY-33.4</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -28744,6 +30963,11 @@
           <t>src/expansion/expansion_engine.py; src/runtime/backtest_v2.py; src/governance/shadow_promotion_gate.py</t>
         </is>
       </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>STORY-21.3</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
@@ -28791,6 +31015,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>STORY-14.3; STORY-21.1</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -28838,6 +31067,11 @@
           <t>src/utils/jsonl_writer.py</t>
         </is>
       </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>STORY-3.1; STORY-3.2; STORY-4.2; STORY-4.3; STORY-4.4; STORY-7.3; STORY-9.1; STORY-10.2; STORY-10.3; STORY-18.1; STORY-21.1; STORY-23.1; STORY-31.22; STORY-32.1; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
@@ -28885,6 +31119,11 @@
           <t>src/governance/framework_registry.py; src/utils/jsonl_writer.py</t>
         </is>
       </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>STORY-18.8; STORY-21.1; STORY-33.9; STORY-36.12; STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -28932,6 +31171,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>STORY-14.3</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -28979,6 +31223,11 @@
           <t>src/identity/tokens.py</t>
         </is>
       </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>STORY-14.3</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -29167,6 +31416,11 @@
           <t>src/governance/bitnet_governance_executor.py; src/governance/reflection_buffer_advanced.py; src/governance/shadow_promotion_gate.py</t>
         </is>
       </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-14.10; STORY-18.12; STORY-33.20; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -29214,6 +31468,11 @@
           <t>src/runtime/backtest_v2.py; src/config_layer/config_builder.py; src/config_layer/production_config.py; src/config_layer/state_identity.py</t>
         </is>
       </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-18.12; STORY-21.3; STORY-30.5; STORY-36.5</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
@@ -29402,6 +31661,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>STORY-14.8</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -29496,6 +31760,11 @@
           <t>src/governance/framework_registry.py; src/utils/jsonl_writer.py; src/control_plane/registry.py</t>
         </is>
       </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>STORY-41.31</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
@@ -29543,6 +31812,11 @@
           <t>src/governance/script_registry.py; src/utils/jsonl_writer.py</t>
         </is>
       </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>STORY-31.22</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -29590,6 +31864,11 @@
           <t>src/governance/framework_registry.py; src/governance/semantic_os.py; src/governance/semantic_query.py; src/governance/jsonl_claim_catalog.py; src/governance/__init__.py; src/governance/measurement_res</t>
         </is>
       </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>STORY-14.3; STORY-20.16; STORY-23.2; STORY-25.12; STORY-25.24; STORY-31.8; STORY-31.20; STORY-33.5; STORY-36.2; STORY-44.4; STORY-45.2</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -29637,6 +31916,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>STORY-31.19</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -29684,6 +31968,11 @@
           <t>src/governance/semantic_os.py; src/governance/semantic_identity.py</t>
         </is>
       </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>STORY-31.19; STORY-31.22</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -29731,6 +32020,11 @@
           <t>src/governance/framework_registry.py</t>
         </is>
       </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>STORY-14.3; STORY-31.5; STORY-31.19; STORY-31.22; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -29778,6 +32072,11 @@
           <t>src/governance/semantic_os.py; src/governance/semantic_objects.py</t>
         </is>
       </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>STORY-31.22</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -29825,6 +32124,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>STORY-14.2; STORY-14.8; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -29870,6 +32174,11 @@
       <c r="I624" s="2" t="inlineStr">
         <is>
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/data_ingestion/ohlcv_schema.py; src/strategies/strategy_orchestrator.py; src/utils/logging_config.py</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-25.21</t>
         </is>
       </c>
     </row>
@@ -29950,6 +32259,11 @@
           <t>src/identity/hashes.py; src/identity/outcome.py; src/identity/query.py; src/identity/store.py; src/identity/tokens.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/features/fe</t>
         </is>
       </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>STORY-20.20</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -29989,6 +32303,11 @@
           <t>src/identity/hashes.py; src/identity/tokens.py</t>
         </is>
       </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>STORY-20.20</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -30106,6 +32425,11 @@
           <t>src/identity/check.py; src/identity/store.py; src/identity/tokens.py</t>
         </is>
       </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>STORY-43.4</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -30145,6 +32469,11 @@
           <t>src/identity/check.py; src/identity/hashes.py; src/identity/tokens.py</t>
         </is>
       </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>STORY-20.20; STORY-43.4</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -30184,6 +32513,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>STORY-13.4; STORY-20.20</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
@@ -30231,6 +32565,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-25.13; STORY-29.1; STORY-29.7</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -30278,6 +32617,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-20.31; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -30325,6 +32669,11 @@
           <t>src/inout/live_rail/bar_builder.py; src/inout/live_rail/binance_ws_adapter.py; src/inout/live_rail/config.py; src/inout/live_rail/longport_adapter.py; src/inout/live_rail/ohlcv_replay_port.py; src/ino</t>
         </is>
       </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
@@ -30372,6 +32721,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/inout/live_rail/config.py; src/inout/live_rail/types.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
@@ -30419,6 +32773,11 @@
           <t>src/inout/live_rail/config.py; src/inout/live_rail/resilience.py; src/inout/live_rail/types.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -30466,6 +32825,11 @@
           <t>src/config_layer/production_config.py; src/inout/live_rail/types.py</t>
         </is>
       </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
@@ -30513,6 +32877,11 @@
           <t>src/inout/live_rail/binance_ws_adapter.py; src/inout/live_rail/config.py; src/inout/live_rail/longport_adapter.py; src/inout/live_rail/resilience.py; src/inout/live_rail/tickdb_adapter.py; src/inout/l</t>
         </is>
       </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -30560,6 +32929,11 @@
           <t>src/inout/live_rail/types.py</t>
         </is>
       </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -30607,6 +32981,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/inout/live_rail/config.py; src/inout/live_rail/types.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>STORY-29.4</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -30654,6 +33033,11 @@
           <t>src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -30701,6 +33085,11 @@
           <t>src/data_ingestion/ohlcv_schema.py; src/inout/live_rail/config.py; src/inout/live_rail/types.py; src/utils/logging_config.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -30748,6 +33137,11 @@
           <t>src/config_layer/crt_engine_v2.py; src/data_ingestion/ohlcv_schema.py</t>
         </is>
       </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -30795,6 +33189,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>STORY-25.13; STORY-29.2; STORY-38.1</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -30842,6 +33241,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>STORY-29.1</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -30889,6 +33293,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>STORY-34.2</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -30936,6 +33345,11 @@
           <t>src/research/contracts.py; src/interpreters/contract.py</t>
         </is>
       </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>STORY-34.2</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -31075,6 +33489,11 @@
       <c r="I651" s="2" t="inlineStr">
         <is>
           <t>src/research/indicators.py; src/interpreters/contract.py</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>STORY-20.25; STORY-34.1; STORY-34.2</t>
         </is>
       </c>
     </row>
@@ -31155,6 +33574,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>STORY-25.6; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -31233,6 +33657,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>STORY-14.4</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -31272,6 +33701,11 @@
           <t>src/journal/schema.py; src/core/collector.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-25.32; STORY-30.5; STORY-30.6; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -31311,6 +33745,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -31405,6 +33844,11 @@
           <t>src/config_layer/production_config.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>STORY-25.8; STORY-29.2; STORY-29.3</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -31452,6 +33896,11 @@
           <t>src/core/ultron_live_adapter.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -31497,6 +33946,11 @@
       <c r="I661" s="2" t="inlineStr">
         <is>
           <t>src/config_layer/production_config.py; src/utils/logging_config.py</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>STORY-13.16</t>
         </is>
       </c>
     </row>
@@ -31694,6 +34148,11 @@
           <t>src/llm_research/pattern_extractor.py</t>
         </is>
       </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>STORY-14.8</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -31772,6 +34231,11 @@
           <t>src/utils/logging_config.py; src/config_layer/production_config.py; src/uat/kill_switch.py; src/strategies/strategy_orchestrator.py; src/live/telegram_bridge.py; src/live/mt5_bridge.py</t>
         </is>
       </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="2" t="inlineStr">
@@ -31866,6 +34330,11 @@
           <t>src/msip/market_state_vector.py</t>
         </is>
       </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>STORY-20.4</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -32287,6 +34756,11 @@
       <c r="I679" s="2" t="inlineStr">
         <is>
           <t>src/utils/jsonl_writer.py; src/events/event_fabric.py</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>STORY-41.1</t>
         </is>
       </c>
     </row>
@@ -32328,6 +34802,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>STORY-8.2; STORY-18.1</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
@@ -32367,6 +34846,11 @@
           <t>src/portfolio/exposure_tracker.py; src/portfolio/correlation_engine.py; src/portfolio/capital_policy.py</t>
         </is>
       </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>STORY-32.1; STORY-32.2; STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -32406,6 +34890,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>STORY-32.2</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -32445,6 +34934,11 @@
           <t>src/utils/integrity_events.py; src/config_layer/production_config.py; src/data_ingestion/historical_fetcher.py</t>
         </is>
       </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>STORY-32.2</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -32523,6 +35017,11 @@
           <t>src/portfolio/allocator.py</t>
         </is>
       </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -32562,6 +35061,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -32640,6 +35144,11 @@
           <t>src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>STORY-18.13; STORY-33.13; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
@@ -32679,6 +35188,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>STORY-37.12; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -32718,6 +35232,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
@@ -32757,6 +35276,11 @@
           <t>src/utils/logging_config.py; src/events/event_fabric.py</t>
         </is>
       </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-21.1; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" s="2" t="inlineStr">
@@ -32796,6 +35320,11 @@
           <t>src/utils/integrity_events.py; src/utils/parquet_store.py; src/utils/registry_refresh.py</t>
         </is>
       </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>STORY-1.5; STORY-18.1; STORY-18.11; STORY-18.13; STORY-20.7; STORY-25.32; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
@@ -32835,6 +35364,11 @@
           <t>faiss</t>
         </is>
       </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -32913,6 +35447,11 @@
           <t>src/data_ingestion/ohlcv_schema.py; src/utils/parquet_store.py</t>
         </is>
       </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>STORY-25.21; STORY-41.59</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -32960,6 +35499,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>STORY-34.2</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -33007,6 +35551,11 @@
           <t>src/research/adapters/spine_signal_source.py</t>
         </is>
       </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>STORY-20.26</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
@@ -33054,6 +35603,11 @@
           <t>src/runtime/backtest_v2.py; src/features/feature_pipeline.py; src/features/market_shape.py; src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>STORY-20.26</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -33101,6 +35655,11 @@
           <t>src/config_layer/production_config.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>STORY-16.3; STORY-20.26; STORY-36.10</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -33148,6 +35707,11 @@
           <t>src/utils/parquet_store.py; src/research/indicators.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>STORY-20.4; STORY-36.2; STORY-36.20</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -33195,6 +35759,11 @@
           <t>src/research/measurement/bootstrap.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>STORY-25.36</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
@@ -33242,6 +35811,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -33289,6 +35863,11 @@
           <t>src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>STORY-20.4; STORY-20.25; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -33336,6 +35915,11 @@
           <t>src/research/conditional_entropy_grid.py</t>
         </is>
       </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="inlineStr">
@@ -33383,6 +35967,11 @@
           <t>src/research/conditional_entropy_grid.py; src/research/candle_state/info_robustness.py</t>
         </is>
       </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -33430,6 +36019,11 @@
           <t>src/research/candle_state/encoder.py; src/research/resample.py</t>
         </is>
       </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -33477,6 +36071,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -33524,6 +36123,11 @@
           <t>src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -33571,6 +36175,11 @@
           <t>src/research/clean_labels/builder.py; src/research/clean_labels/protocol.py</t>
         </is>
       </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -33618,6 +36227,11 @@
           <t>src/features/dataset_builder.py; src/features/feature_schema.py; src/research/clean_labels/protocol.py; src/research/contracts.py; src/research/measurement/forward_walk.py</t>
         </is>
       </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="inlineStr">
@@ -33665,6 +36279,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>STORY-16.4; STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="2" t="inlineStr">
@@ -33712,6 +36331,11 @@
           <t>src/research/controls/__init__.py; src/research/hypotheses/__init__.py; src/research/config.py; src/research/registry.py; src/research/runner.py; src/research/provenance.py; src/research/measurement/m</t>
         </is>
       </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>STORY-14.5; STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -33759,6 +36383,11 @@
           <t>src/research/indicators.py; src/research/process_diagnostics.py</t>
         </is>
       </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -33806,6 +36435,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>STORY-25.20; STORY-36.1</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" s="2" t="inlineStr">
@@ -33853,6 +36487,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>STORY-15.1; STORY-34.2</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -33900,6 +36539,11 @@
           <t>src/research/controls/always_long.py; src/research/controls/random_baseline.py; src/research/registry.py</t>
         </is>
       </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>STORY-36.27</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" s="2" t="inlineStr">
@@ -33947,6 +36591,11 @@
           <t>src/research/contracts.py; src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>STORY-36.27</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="2" t="inlineStr">
@@ -33994,6 +36643,11 @@
           <t>src/research/contracts.py; src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>STORY-36.27</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -34041,6 +36695,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-30.3; STORY-31.7; STORY-34.2; STORY-36.19</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="2" t="inlineStr">
@@ -34088,6 +36747,11 @@
           <t>src/research/costs.py; src/research/qualification.py; src/runtime/backtest_v2.py; src/data_ingestion/ohlcv_schema.py</t>
         </is>
       </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>STORY-29.1; STORY-36.19</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -34135,6 +36799,11 @@
           <t>src/research/envelope_offline/shadow.py; src/research/envelope_offline/train.py</t>
         </is>
       </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
@@ -34182,6 +36851,11 @@
           <t>src/research/envelope_offline/train.py</t>
         </is>
       </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="inlineStr">
@@ -34229,6 +36903,11 @@
           <t>src/features/feature_schema.py; src/research/clean_labels/builder.py</t>
         </is>
       </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>STORY-16.4</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
@@ -34276,6 +36955,11 @@
           <t>src/research/episode_propositions.py</t>
         </is>
       </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>STORY-25.16; STORY-25.26</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" s="2" t="inlineStr">
@@ -34323,6 +37007,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>STORY-25.16; STORY-25.26</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" s="2" t="inlineStr">
@@ -34370,6 +37059,11 @@
           <t>src/research/episodes/protocol.py</t>
         </is>
       </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" s="2" t="inlineStr">
@@ -34417,6 +37111,11 @@
           <t>src/research/episodes/protocol.py; src/research/episodes/schema.py; src/research/episodes/builder.py</t>
         </is>
       </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="2" t="inlineStr">
@@ -34464,6 +37163,11 @@
           <t>src/research/episodes/schema.py; src/research/episodes/events.py</t>
         </is>
       </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="2" t="inlineStr">
@@ -34511,6 +37215,11 @@
           <t>src/research/episodes/events.py; src/research/episodes/policy.py; src/research/episodes/schema.py</t>
         </is>
       </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="2" t="inlineStr">
@@ -34558,6 +37267,11 @@
           <t>src/research/contracts.py; src/research/episodes/protocol.py; src/research/episodes/schema.py; src/research/measurement/forward_walk.py; src/research/episodes/policy.py</t>
         </is>
       </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>STORY-31.11</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="inlineStr">
@@ -34605,6 +37319,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="2" t="inlineStr">
@@ -34652,6 +37371,11 @@
           <t>src/research/episodes/builder.py; src/research/episodes/protocol.py; src/research/episodes/schema.py</t>
         </is>
       </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>STORY-31.11</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -34699,6 +37423,11 @@
           <t>src/research/episodes/builder.py; src/research/episodes/protocol.py; src/research/episodes/schema.py</t>
         </is>
       </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="inlineStr">
@@ -34746,6 +37475,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>STORY-30.1; STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="inlineStr">
@@ -34793,6 +37527,11 @@
           <t>src/research/episodes/events.py; src/research/episodes/policy.py; src/research/episodes/protocol.py; src/research/episodes/schema.py</t>
         </is>
       </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="inlineStr">
@@ -34840,6 +37579,11 @@
           <t>src/research/episodes/protocol.py</t>
         </is>
       </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>STORY-25.6</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="2" t="inlineStr">
@@ -34887,6 +37631,11 @@
           <t>src/research/episodes/protocol.py; src/research/episodes/schema.py</t>
         </is>
       </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" s="2" t="inlineStr">
@@ -34934,6 +37683,11 @@
           <t>src/research/episodes/schema.py</t>
         </is>
       </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -34981,6 +37735,11 @@
           <t>src/research/evidence/catalog.py; src/research/evidence/atlases.py; src/research/evidence/queries.py; src/research/evidence/records.py</t>
         </is>
       </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="inlineStr">
@@ -35028,6 +37787,11 @@
           <t>src/research/evidence/driver.py</t>
         </is>
       </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="inlineStr">
@@ -35075,6 +37839,11 @@
           <t>src/data_ingestion/dataset_integrity.py; src/research/evidence/run_close_out.py; src/research/evidence/catalog.py; src/research/evidence/driver.py; src/research/evidence/queries.py</t>
         </is>
       </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
@@ -35122,6 +37891,11 @@
           <t>src/research/evidence/queries.py; src/research/evidence/records.py</t>
         </is>
       </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="2" t="inlineStr">
@@ -35169,6 +37943,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>STORY-25.4; STORY-25.17</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -35216,6 +37995,11 @@
           <t>src/research/evidence/catalog.py; src/research/evidence/queries.py; src/research/evidence/records.py; src/utils/parquet_store.py</t>
         </is>
       </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -35263,6 +38047,11 @@
           <t>src/data_ingestion/dataset_integrity.py; src/research/evidence/run_close_out.py; src/research/evidence/asymmetry_contract.py; src/research/evidence/catalog.py; src/research/evidence/driver.py; src/res</t>
         </is>
       </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
@@ -35310,6 +38099,11 @@
           <t>src/data_ingestion/dataset_integrity.py; src/research/evidence/run_close_out.py; src/research/evidence/asymmetry_contract.py; src/research/evidence/catalog.py; src/research/evidence/driver.py; src/res</t>
         </is>
       </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -35357,6 +38151,11 @@
           <t>src/research/evidence/catalog.py; src/research/evidence/records.py; src/research/evidence/atlases.py</t>
         </is>
       </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="inlineStr">
@@ -35404,6 +38203,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="inlineStr">
@@ -35451,6 +38255,11 @@
           <t>src/data_ingestion/dataset_integrity.py; src/research/evidence/run_close_out.py; src/research/evidence/catalog.py; src/research/evidence/driver.py; src/research/evidence/magnitude_prior.py; src/resear</t>
         </is>
       </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" s="2" t="inlineStr">
@@ -35498,6 +38307,11 @@
           <t>src/research/measurement/mt00.py; src/research/provenance.py; src/utils/run_manifest.py; src/utils/validation_contract.py</t>
         </is>
       </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>STORY-36.25</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="inlineStr">
@@ -35545,6 +38359,11 @@
           <t>src/research/contracts.py; src/research/costs.py; src/research/measurement/forward_walk.py</t>
         </is>
       </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>STORY-30.1; STORY-30.6; STORY-36.22</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="inlineStr">
@@ -35592,6 +38411,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="inlineStr">
@@ -35639,6 +38463,11 @@
           <t>src/research/config.py; src/research/costs.py; src/research/indicators.py; src/research/measurement/forward_walk.py; src/research/provenance.py; src/research/registry.py; src/runtime/backtest_v2.py</t>
         </is>
       </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>STORY-30.1; STORY-31.11</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="2" t="inlineStr">
@@ -35686,6 +38515,11 @@
           <t>src/config_layer/goal_schema.py; src/config_layer/goal_validator.py; src/research/contracts.py</t>
         </is>
       </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>STORY-27.1; STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="2" t="inlineStr">
@@ -35733,6 +38567,11 @@
           <t>src/research/hypotheses/__init__.py</t>
         </is>
       </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" s="2" t="inlineStr">
@@ -35780,6 +38619,11 @@
           <t>src/research/candle_state/encoder.py; src/research/contracts.py; src/research/indicators.py; src/research/registry.py</t>
         </is>
       </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>STORY-36.1; STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="2" t="inlineStr">
@@ -35827,6 +38671,11 @@
           <t>src/research/contracts.py; src/research/indicators.py; src/research/registry.py</t>
         </is>
       </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>STORY-23.3</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="2" t="inlineStr">
@@ -35874,6 +38723,11 @@
           <t>src/research/contracts.py; src/research/indicators.py; src/research/registry.py; src/research/adapters/shape_signal_source.py</t>
         </is>
       </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>STORY-36.8; STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="inlineStr">
@@ -35921,6 +38775,11 @@
           <t>src/research/contracts.py; src/research/indicators.py; src/research/registry.py</t>
         </is>
       </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>STORY-41.64</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" s="2" t="inlineStr">
@@ -35968,6 +38827,11 @@
           <t>src/research/contracts.py; src/research/indicators.py; src/research/registry.py; src/research/adapters/spine_signal_source.py</t>
         </is>
       </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>STORY-36.10</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -36015,6 +38879,11 @@
           <t>src/interpreters/regime_observer.py; src/research/candle_state/encoder.py; src/research/contracts.py; src/research/indicators.py; src/research/registry.py; src/research/weekly_sweep/weekly_range.py</t>
         </is>
       </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>STORY-41.65</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="inlineStr">
@@ -36062,6 +38931,11 @@
           <t>src/research/ic002_entry_evolution/schema.py</t>
         </is>
       </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="inlineStr">
@@ -36109,6 +38983,11 @@
           <t>src/research/ic002_entry_evolution/io_util.py; src/research/ic002_entry_evolution/schema.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" s="2" t="inlineStr">
@@ -36156,6 +39035,11 @@
           <t>src/research/ic002_entry_evolution/io_util.py; src/research/ic002_entry_evolution/schema.py</t>
         </is>
       </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" s="2" t="inlineStr">
@@ -36203,6 +39087,11 @@
           <t>src/research/ic002_entry_evolution/schema.py</t>
         </is>
       </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="inlineStr">
@@ -36250,6 +39139,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>STORY-30.1</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="2" t="inlineStr">
@@ -36297,6 +39191,11 @@
           <t>src/research/ic003_shapes/schema.py</t>
         </is>
       </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>STORY-41.61</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" s="2" t="inlineStr">
@@ -36344,6 +39243,11 @@
           <t>src/research/ic002_entry_evolution/io_util.py; src/research/ic002_entry_evolution/schema.py; src/research/ic003_shapes/schema.py</t>
         </is>
       </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>STORY-41.61</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" s="2" t="inlineStr">
@@ -36391,6 +39295,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>STORY-41.61</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="2" t="inlineStr">
@@ -36438,6 +39347,11 @@
           <t>src/research/ic003b_sequence_geometry/schema.py</t>
         </is>
       </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="2" t="inlineStr">
@@ -36485,6 +39399,11 @@
           <t>src/research/ic002_entry_evolution/io_util.py; src/research/ic002_entry_evolution/schema.py; src/research/ic003b_sequence_geometry/cluster_dtw.py; src/research/ic003b_sequence_geometry/cluster_euclid.</t>
         </is>
       </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="2" t="inlineStr">
@@ -36532,6 +39451,11 @@
           <t>src/research/ic003b_sequence_geometry/dtw.py; src/research/ic003b_sequence_geometry/schema.py</t>
         </is>
       </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="2" t="inlineStr">
@@ -36579,6 +39503,11 @@
           <t>src/research/ic003b_sequence_geometry/schema.py</t>
         </is>
       </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="2" t="inlineStr">
@@ -36626,6 +39555,11 @@
           <t>src/research/ic003b_sequence_geometry/schema.py</t>
         </is>
       </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="inlineStr">
@@ -36673,6 +39607,11 @@
           <t>src/research/ic003b_sequence_geometry/schema.py</t>
         </is>
       </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="inlineStr">
@@ -36720,6 +39659,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="inlineStr">
@@ -36767,6 +39711,11 @@
           <t>src/research/ic003b_sequence_geometry/schema.py</t>
         </is>
       </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>STORY-41.6</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="2" t="inlineStr">
@@ -36814,6 +39763,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>STORY-23.3; STORY-36.17; STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" s="2" t="inlineStr">
@@ -36861,6 +39815,11 @@
           <t>src/research/measurement/forward_walk.py; src/research/measurement/metrics.py</t>
         </is>
       </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>STORY-36.11</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="2" t="inlineStr">
@@ -36908,6 +39867,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>STORY-20.26; STORY-36.8</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="2" t="inlineStr">
@@ -36955,6 +39919,11 @@
           <t>src/research/contracts.py</t>
         </is>
       </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>STORY-15.1; STORY-20.26; STORY-30.1; STORY-30.3; STORY-30.6; STORY-31.7; STORY-31.11; STORY-33.7; STORY-34.2; STORY-36.1; STORY-36.17; STORY-36.22; STORY-37.3</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" s="2" t="inlineStr">
@@ -37002,6 +39971,11 @@
           <t>src/research/contracts.py; src/research/costs.py</t>
         </is>
       </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>STORY-20.26; STORY-20.29; STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" s="2" t="inlineStr">
@@ -37049,6 +40023,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>STORY-36.11</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" s="2" t="inlineStr">
@@ -37096,6 +40075,11 @@
           <t>src/research/model_runners/contracts.py; src/research/model_runners/runner.py</t>
         </is>
       </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" s="2" t="inlineStr">
@@ -37143,6 +40127,11 @@
           <t>src/research/model_runners/contracts.py; src/research/model_runners/substrate.py; src/research/model_runners/adapters/rr_polarity.py; src/research/model_runners/adapters/dual_engine.py; src/research/m</t>
         </is>
       </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">
@@ -37190,6 +40179,11 @@
           <t>src/bitnet/bitnet_inference.py; src/bitnet/defaults.py; src/research/model_runners/contracts.py; src/research/model_runners/substrate.py; src/research/model_runners/require_config.py</t>
         </is>
       </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" s="2" t="inlineStr">
@@ -37237,6 +40231,11 @@
           <t>src/engines/crt_engine.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/substrate.py</t>
         </is>
       </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" s="2" t="inlineStr">
@@ -37284,6 +40283,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/crt_engine_v2.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/substrate.py; s</t>
         </is>
       </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" s="2" t="inlineStr">
@@ -37331,6 +40335,11 @@
           <t>src/core/decision_engine.py; src/research/model_runners/adapters/fusion_compute.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/su</t>
         </is>
       </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" s="2" t="inlineStr">
@@ -37378,6 +40387,11 @@
           <t>src/core/engine_runner.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/substrate.py</t>
         </is>
       </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="2" t="inlineStr">
@@ -37425,6 +40439,11 @@
           <t>src/research/envelope_offline/shadow.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/schema_resolver.py; src/research/model_runner</t>
         </is>
       </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" s="2" t="inlineStr">
@@ -37472,6 +40491,11 @@
           <t>src/config_layer/execution_planner.py; src/core/engine_runner.py; src/core/gate_intelligence.py; src/research/model_runners/adapters/decision.py; src/research/model_runners/contracts.py; src/research/</t>
         </is>
       </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>STORY-29.2; STORY-31.23</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" s="2" t="inlineStr">
@@ -37519,6 +40543,11 @@
           <t>src/core/fusion_engine.py; src/research/model_runners/adapters/crt_score.py; src/research/model_runners/adapters/gaussian.py; src/research/model_runners/adapters/rr_polarity.py; src/research/model_run</t>
         </is>
       </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="2" t="inlineStr">
@@ -37566,6 +40595,11 @@
           <t>src/engines/heuristic_gaussian_engine.py; src/features/feature_schema.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/substrate.py</t>
         </is>
       </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="inlineStr">
@@ -37613,6 +40647,11 @@
           <t>src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/schema_resolver.py; src/research/model_runners/substrate.py; src/training/trainer.py</t>
         </is>
       </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="2" t="inlineStr">
@@ -37660,6 +40699,11 @@
           <t>src/engines/rr_engine.py; src/research/model_runners/contracts.py; src/research/model_runners/substrate.py</t>
         </is>
       </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="2" t="inlineStr">
@@ -37707,6 +40751,11 @@
           <t>src/config_layer/rr/rr_pattern_miner.py; src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/schema_resolver.py; src/research/model_runner</t>
         </is>
       </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="2" t="inlineStr">
@@ -37754,6 +40803,11 @@
           <t>src/research/model_runners/contracts.py; src/research/model_runners/require_config.py; src/research/model_runners/substrate.py; src/training/trade_net_v2.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" s="2" t="inlineStr">
@@ -37801,6 +40855,11 @@
           <t>src/config_layer/model_resolver.py; src/engines/live_engine.py; src/engines/zone_cluster_score.py; src/features/feature_schema.py; src/research/model_runners/contracts.py; src/research/model_runners/r</t>
         </is>
       </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" s="2" t="inlineStr">
@@ -37848,6 +40907,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" s="2" t="inlineStr">
@@ -37895,6 +40959,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="2" t="inlineStr">
@@ -37942,6 +41011,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="2" t="inlineStr">
@@ -37989,6 +41063,11 @@
           <t>src/research/model_runners/adapters/__init__.py; src/research/model_runners/contracts.py; src/research/model_runners/envelope.py; src/research/model_runners/require_config.py; src/research/model_runne</t>
         </is>
       </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="2" t="inlineStr">
@@ -38036,6 +41115,11 @@
           <t>src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="2" t="inlineStr">
@@ -38083,6 +41167,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" s="2" t="inlineStr">
@@ -38130,6 +41219,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/research/model_runners/require_config.py</t>
         </is>
       </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>STORY-41.29</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="2" t="inlineStr">
@@ -38177,6 +41271,11 @@
           <t>src/research/mother_range/geometry.py</t>
         </is>
       </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>STORY-36.7</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" s="2" t="inlineStr">
@@ -38224,6 +41323,11 @@
           <t>src/research/mother_range/driver.py</t>
         </is>
       </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>STORY-36.7</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" s="2" t="inlineStr">
@@ -38271,6 +41375,11 @@
           <t>src/data_ingestion/dataset_integrity.py; src/research/contracts.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/mother_range/geometry.py</t>
         </is>
       </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>STORY-36.7</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" s="2" t="inlineStr">
@@ -38318,6 +41427,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>STORY-36.7</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" s="2" t="inlineStr">
@@ -38365,6 +41479,11 @@
           <t>mt5_analytics.core.mt5_adapter</t>
         </is>
       </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>STORY-38.1</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" s="2" t="inlineStr">
@@ -38412,6 +41531,11 @@
           <t>src/research/oracle/multi_tp_walk.py; src/research/oracle/reference_walker.py</t>
         </is>
       </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" s="2" t="inlineStr">
@@ -38459,6 +41583,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>STORY-31.11</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" s="2" t="inlineStr">
@@ -38506,6 +41635,11 @@
           <t>src/research/oracle/labeler.py; src/research/oracle/multi_tp_walk.py; src/research/oracle/stop_policy.py</t>
         </is>
       </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" s="2" t="inlineStr">
@@ -38553,6 +41687,11 @@
           <t>src/config_layer/production_config.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/oracle/multi_tp_walk.py</t>
         </is>
       </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" s="2" t="inlineStr">
@@ -38600,6 +41739,11 @@
           <t>src/research/oracle/stop_policy.py</t>
         </is>
       </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>STORY-41.11</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" s="2" t="inlineStr">
@@ -38647,6 +41791,11 @@
           <t>src/research/oracle/multi_tp_walk.py</t>
         </is>
       </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" s="2" t="inlineStr">
@@ -38694,6 +41843,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>STORY-41.21</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="inlineStr">
@@ -38741,6 +41895,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>STORY-41.11</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="inlineStr">
@@ -38788,6 +41947,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>STORY-36.22</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="2" t="inlineStr">
@@ -38835,6 +41999,11 @@
           <t>src/research/contracts.py; src/research/exit_grid.py; src/research/measurement/forward_walk.py</t>
         </is>
       </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>STORY-36.22</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" s="2" t="inlineStr">
@@ -38882,6 +42051,11 @@
           <t>src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>STORY-34.1; STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="inlineStr">
@@ -38929,6 +42103,11 @@
           <t>src/research/process_characterization.py</t>
         </is>
       </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>STORY-36.17</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" s="2" t="inlineStr">
@@ -38976,6 +42155,11 @@
           <t>src/config_layer/production_config.py; src/features/feature_schema.py</t>
         </is>
       </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>STORY-25.20; STORY-30.5; STORY-36.19</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" s="2" t="inlineStr">
@@ -39023,6 +42207,11 @@
           <t>src/research/contracts.py; src/research/costs.py; src/research/measurement/metrics.py</t>
         </is>
       </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>STORY-20.26; STORY-21.1; STORY-25.13; STORY-27.2; STORY-30.3; STORY-30.6; STORY-31.7; STORY-34.2; STORY-36.8; STORY-36.14; STORY-36.17; STORY-36.19; STORY-36.22; STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="2" t="inlineStr">
@@ -39070,6 +42259,11 @@
           <t>src/research/contracts.py; src/research/costs.py; src/research/measurement/metrics.py; src/research/qualification.py</t>
         </is>
       </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>STORY-34.1; STORY-34.2; STORY-36.18</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="2" t="inlineStr">
@@ -39117,6 +42311,11 @@
           <t>src/research/contracts.py</t>
         </is>
       </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>STORY-21.1; STORY-36.10</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" s="2" t="inlineStr">
@@ -39164,6 +42363,11 @@
           <t>src/research/config.py; src/research/contracts.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/measurement/metrics.py; src/research/provenance.py; src/research/regist</t>
         </is>
       </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>STORY-20.29; STORY-36.1; STORY-36.8; STORY-36.17; STORY-36.19; STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" s="2" t="inlineStr">
@@ -39211,6 +42415,11 @@
           <t>src/research/secondlow_v1/corpus.py; src/research/secondlow_v1/detector.py</t>
         </is>
       </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>STORY-25.8</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" s="2" t="inlineStr">
@@ -39258,6 +42467,11 @@
           <t>src/data_ingestion/xauusd_phase1_candidate.py</t>
         </is>
       </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>STORY-25.8</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -39305,6 +42519,11 @@
           <t>src/research/secondlow_v1/detector.py</t>
         </is>
       </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>STORY-25.8</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -39352,6 +42571,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>STORY-25.8</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="inlineStr">
@@ -39399,6 +42623,11 @@
           <t>src/research/secondlow_v1/detector.py</t>
         </is>
       </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>STORY-25.8</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="inlineStr">
@@ -39446,6 +42675,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>STORY-30.3</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="inlineStr">
@@ -39493,6 +42727,11 @@
           <t>src/features/market_shape.py; src/research/measurement/bootstrap.py; src/features/feature_pipeline.py</t>
         </is>
       </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>STORY-36.8; STORY-36.12</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="2" t="inlineStr">
@@ -39540,6 +42779,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>STORY-36.20</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="inlineStr">
@@ -39587,6 +42831,11 @@
           <t>src/research/synthetic/story_spec.py</t>
         </is>
       </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" s="2" t="inlineStr">
@@ -39634,6 +42883,11 @@
           <t>src/features/feature_schema.py; src/config_layer/state_identity.py; src/config_layer/state_topology.py</t>
         </is>
       </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="839">
       <c r="A839" s="2" t="inlineStr">
@@ -39681,6 +42935,11 @@
           <t>src/research/synthetic/stories/breakout.py; src/research/synthetic/stories/liquidity_reversal.py; src/research/synthetic/stories/range_rotation.py; src/research/synthetic/stories/trend_continuation.py</t>
         </is>
       </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" s="2" t="inlineStr">
@@ -39728,6 +42987,11 @@
           <t>src/research/synthetic/story_spec.py</t>
         </is>
       </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" s="2" t="inlineStr">
@@ -39775,6 +43039,11 @@
           <t>src/research/synthetic/story_spec.py</t>
         </is>
       </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" s="2" t="inlineStr">
@@ -39822,6 +43091,11 @@
           <t>src/research/synthetic/story_spec.py</t>
         </is>
       </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="2" t="inlineStr">
@@ -39869,6 +43143,11 @@
           <t>src/research/synthetic/story_spec.py</t>
         </is>
       </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" s="2" t="inlineStr">
@@ -39916,6 +43195,11 @@
           <t>src/data_ingestion/ohlcv_schema.py; src/engines/crt_engine.py; src/engines/heuristic_gaussian_engine.py; src/engines/rr_engine.py; src/engines/scoring_engine.py; src/engines/zone_gate_engine.py; src/f</t>
         </is>
       </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="inlineStr">
@@ -39963,6 +43247,11 @@
           <t>src/research/synthetic/stories/__init__.py; src/research/synthetic/story_spec.py</t>
         </is>
       </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="inlineStr">
@@ -40010,6 +43299,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>STORY-41.60</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="inlineStr">
@@ -40057,6 +43351,11 @@
           <t>src/research/visual_crt/geometry.py; src/research/visual_crt/pools.py</t>
         </is>
       </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="inlineStr">
@@ -40104,6 +43403,11 @@
           <t>src/research/contracts.py; src/research/measurement/forward_walk.py; src/research/visual_crt/driver.py; src/research/indicators.py</t>
         </is>
       </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
@@ -40151,6 +43455,11 @@
           <t>src/features/parent_candle.py; src/research/contracts.py; src/research/indicators.py; src/research/measurement/forward_walk.py; src/research/visual_crt/geometry.py; src/research/visual_crt/pools.py; s</t>
         </is>
       </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>STORY-20.2; STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="inlineStr">
@@ -40198,6 +43507,11 @@
           <t>src/features/candle_math.py; src/structure/predicates.py; src/research/visual_crt/pools.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>STORY-36.2; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" s="2" t="inlineStr">
@@ -40245,6 +43559,11 @@
           <t>src/research/costs.py; src/research/measurement/forward_walk.py; src/research/provenance.py; src/research/visual_crt/controls.py; src/research/visual_crt/driver.py; src/data_ingestion/dataset_integrit</t>
         </is>
       </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -40292,6 +43611,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>STORY-36.4</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
@@ -40339,6 +43663,11 @@
           <t>src/research/visual_crt/geometry.py; src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>STORY-20.2; STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="inlineStr">
@@ -40386,6 +43715,11 @@
           <t>src/research/weekly_sweep/weekly_range.py</t>
         </is>
       </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -40433,6 +43767,11 @@
           <t>src/structure/predicates.py; src/config_layer/crt_engine_v2.py; src/data_ingestion/session_autoderive.py</t>
         </is>
       </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>STORY-36.2; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -40480,6 +43819,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>STORY-37.9</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="inlineStr">
@@ -40527,6 +43871,11 @@
           <t>src/bitnet/zone_cosine_searcher.py; src/research/contracts.py; src/research/measurement/forward_walk.py</t>
         </is>
       </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>STORY-37.3</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="inlineStr">
@@ -40574,6 +43923,11 @@
           <t>src/research/zone_mapping/historical_zone_mapper.py; src/research/zone_mapping/zone_census.py</t>
         </is>
       </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
@@ -40621,6 +43975,11 @@
           <t>src/research/zone_mapping/crt_zone_crosstab.py; src/research/zone_mapping/displacement_zone_event_study.py</t>
         </is>
       </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="inlineStr">
@@ -40668,6 +44027,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/research/zone_mapping/historical_zone_mapper.py; src/research/zone_mapping/zone_census.py</t>
         </is>
       </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="inlineStr">
@@ -40715,6 +44079,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/crt_engine_v2.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/runtime/backtest_v2.py; src/config_layer/production_config.</t>
         </is>
       </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" s="2" t="inlineStr">
@@ -40762,6 +44131,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/crt_engine_v2.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/research/zone_mapping/collect_trade_opened_features.py; src</t>
         </is>
       </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" s="2" t="inlineStr">
@@ -40809,6 +44183,11 @@
           <t>src/research/zone_mapping/crt_zone_crosstab.py</t>
         </is>
       </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>STORY-36.2</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" s="2" t="inlineStr">
@@ -40856,6 +44235,11 @@
           <t>src/research/contracts.py; src/research/costs.py; src/research/measurement/forward_walk.py; src/research/zone_mapping/gaussian_family_shadow_eval.py; src/research/zone_mapping/rare_zone_detection_eval</t>
         </is>
       </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
@@ -40903,6 +44287,11 @@
           <t>src/config_layer/config_builder.py; src/config_layer/crt_engine_v2.py; src/engines/heuristic_gaussian_engine.py; src/engines/ml_gaussian_engine.py; src/features/feature_pipeline.py; src/features/featu</t>
         </is>
       </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" s="2" t="inlineStr">
@@ -40950,6 +44339,11 @@
           <t>src/features/feature_schema.py; src/engines/live_engine.py; src/engines/zone_cluster_score.py; src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" s="2" t="inlineStr">
@@ -40997,6 +44391,11 @@
           <t>src/research/zone_mapping/crt_zone_crosstab.py; src/research/zone_mapping/displacement_zone_event_study.py; src/research/zone_mapping/rare_zone_detection_eval.py</t>
         </is>
       </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="inlineStr">
@@ -41044,6 +44443,11 @@
           <t>src/research/zone_mapping/crt_zone_crosstab.py; src/research/zone_mapping/displacement_zone_event_study.py</t>
         </is>
       </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="2" t="inlineStr">
@@ -41091,6 +44495,11 @@
           <t>src/research/zone_mapping/crt_zone_crosstab.py; src/research/zone_mapping/displacement_zone_event_study.py; src/research/zone_mapping/rare_zone_detection_eval.py</t>
         </is>
       </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -41136,6 +44545,11 @@
       <c r="I870" s="2" t="inlineStr">
         <is>
           <t>(none / stdlib-only)</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>STORY-37.4</t>
         </is>
       </c>
     </row>
@@ -41177,6 +44591,11 @@
           <t>src/retrieval/config.py; src/retrieval/chunking.py; src/retrieval/embedding.py; src/retrieval/vector_store.py; src/retrieval/corpus.py; src/retrieval/retriever.py; src/retrieval/monitor.py</t>
         </is>
       </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>STORY-19.3; STORY-25.34</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="inlineStr">
@@ -41216,6 +44635,11 @@
           <t>src/retrieval/config.py; src/retrieval/corpus.py</t>
         </is>
       </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>STORY-25.35</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
@@ -41255,6 +44679,11 @@
           <t>src/retrieval/__init__.py; src/retrieval/config.py; src/retrieval/retriever.py</t>
         </is>
       </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>STORY-14.4</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -41294,6 +44723,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-18.8; STORY-19.3</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="inlineStr">
@@ -41372,6 +44806,11 @@
           <t>src/retrieval/config.py</t>
         </is>
       </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>STORY-25.34</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="inlineStr">
@@ -41411,6 +44850,11 @@
           <t>src/retrieval/config.py</t>
         </is>
       </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-19.9; STORY-25.35</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="inlineStr">
@@ -41450,6 +44894,11 @@
           <t>src/retrieval/config.py; src/retrieval/vector_store.py</t>
         </is>
       </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>STORY-19.8; STORY-25.34</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" s="2" t="inlineStr">
@@ -41489,6 +44938,11 @@
           <t>src/retrieval/config.py; src/retrieval/chunking.py; src/retrieval/corpus.py; src/retrieval/embedding.py</t>
         </is>
       </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>STORY-25.24; STORY-25.34</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="inlineStr">
@@ -41583,6 +45037,11 @@
           <t>src/utils/console_safe.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>STORY-18.12; STORY-25.32</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" s="2" t="inlineStr">
@@ -41630,6 +45089,11 @@
           <t>src/core/engine_runner.py; src/features/feature_pipeline.py; src/features/feature_schema.py; src/utils/console_safe.py; src/bitnet/bitnet_runner.py</t>
         </is>
       </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-14.10; STORY-16.5; STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" s="2" t="inlineStr">
@@ -41677,6 +45141,11 @@
           <t>src/utils/console_safe.py; src/features/feature_schema.py; src/core/model_registry.py; src/config_layer/production_config.py; src/config_layer/production_bundle.py; src/config_layer/stack_version.py</t>
         </is>
       </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>STORY-18.7; STORY-18.12; STORY-20.25; STORY-31.9; STORY-35.1; STORY-37.12</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="inlineStr">
@@ -41724,6 +45193,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>STORY-31.6</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="inlineStr">
@@ -41865,6 +45339,11 @@
           <t>src/features/feature_pipeline.py; src/features/feature_schema.py; src/inout/live_rail/types.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
@@ -41912,6 +45391,11 @@
           <t>src/config_layer/production_config.py; src/core/ultron_live_adapter.py; src/core/ultron_risk_gate.py; src/engines/live_engine.py; src/inout/live_rail/bar_builder.py; src/inout/live_rail/config.py; src</t>
         </is>
       </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>STORY-12.5; STORY-20.16; STORY-29.2; STORY-29.4</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
@@ -41959,6 +45443,11 @@
           <t>src/config_layer/htf_state.py; src/config_layer/parent_crt.py; src/config_layer/production_config.py; src/config_layer/state_identity.py; src/features/parent_candle.py</t>
         </is>
       </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>STORY-25.12; STORY-29.2; STORY-31.20</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
@@ -42004,6 +45493,11 @@
       <c r="I890" s="2" t="inlineStr">
         <is>
           <t>src/config_layer/config_builder.py; src/runtime/backtest_bitnet.py; src/runtime/backtest_v2.py; src/utils/console_safe.py; src/config_layer/production_config.py</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>STORY-14.8; STORY-18.12; STORY-21.3; STORY-30.5</t>
         </is>
       </c>
     </row>
@@ -42123,6 +45617,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>STORY-36.5</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="2" t="inlineStr">
@@ -42162,6 +45661,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>STORY-32.2</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" s="2" t="inlineStr">
@@ -42240,6 +45744,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>STORY-36.5</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" s="2" t="inlineStr">
@@ -42357,6 +45866,11 @@
           <t>src/config_layer/production_config.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>STORY-21.3</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
@@ -42396,6 +45910,11 @@
           <t>src/strategies/strategy_intent.py; src/strategies/strategy_result.py</t>
         </is>
       </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>STORY-18.11</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="2" t="inlineStr">
@@ -42435,6 +45954,11 @@
           <t>src/config_layer/production_config.py; src/engines/__init__.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-18.11; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" s="2" t="inlineStr">
@@ -42474,6 +45998,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" s="2" t="inlineStr">
@@ -42513,6 +46042,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="2" t="inlineStr">
@@ -42552,6 +46086,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" s="2" t="inlineStr">
@@ -42591,6 +46130,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="2" t="inlineStr">
@@ -42630,6 +46174,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
@@ -42669,6 +46218,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
@@ -42708,6 +46262,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py; src/bitnet/bitnet_inference.py</t>
         </is>
       </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
@@ -42747,6 +46306,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
@@ -42786,6 +46350,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/strategy_result.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>STORY-3.2; STORY-18.1; STORY-18.11; STORY-23.1</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -42825,6 +46394,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>STORY-18.11</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -42864,6 +46438,11 @@
           <t>src/config_layer/production_config.py; src/strategies/base_strategy.py; src/strategies/intent_builder.py; src/strategies/strategy_intent.py; src/strategies/strategy_result.py; src/strategies/s01_crt_w</t>
         </is>
       </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>STORY-5.2; STORY-18.1; STORY-18.10; STORY-18.11; STORY-41.33; STORY-41.51; STORY-41.57</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
@@ -42903,6 +46482,11 @@
           <t>src/config_layer/production_config.py; src/features/feature_schema.py; src/core/__init__.py</t>
         </is>
       </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>STORY-25.20; STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
@@ -42942,6 +46526,11 @@
           <t>src/strategies/strategy_package.py</t>
         </is>
       </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>STORY-30.5</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
@@ -42981,6 +46570,11 @@
           <t>src/strategies/strategy_intent.py</t>
         </is>
       </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>STORY-18.11; STORY-21.2</t>
+        </is>
+      </c>
     </row>
     <row r="916">
       <c r="A916" s="2" t="inlineStr">
@@ -43059,6 +46653,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>STORY-20.17; STORY-36.2; STORY-36.23</t>
+        </is>
+      </c>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
@@ -43137,6 +46736,11 @@
           <t>src/features/dataset_builder.py</t>
         </is>
       </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>STORY-35.2; STORY-37.12</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
@@ -43176,6 +46780,11 @@
           <t>src/config_layer/production_config.py; src/training/evaluator.py; src/training/trainer.py</t>
         </is>
       </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>STORY-33.1; STORY-37.11; STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" s="2" t="inlineStr">
@@ -43215,6 +46824,11 @@
           <t>src/features/feature_schema.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>STORY-31.11; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -43254,6 +46868,11 @@
           <t>src/core/model_registry.py; src/features/feature_schema.py; src/training/trainer.py; src/features/dataset_builder.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>STORY-25.23; STORY-33.1; STORY-38.2</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" s="2" t="inlineStr">
@@ -43293,6 +46912,11 @@
           <t>src/features/dataset_validator.py; src/features/feature_schema.py; src/features/dataset_builder.py; src/training/trainer.py; src/training/evaluator.py; src/training/phase5_calibration.py; src/core/mod</t>
         </is>
       </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>STORY-37.13; STORY-38.6; STORY-47.3</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" s="2" t="inlineStr">
@@ -43332,6 +46956,11 @@
           <t>src/features/feature_schema.py; src/features/dataset_builder.py; src/features/gaussian_schema_contract.py; src/core/model_registry.py; src/utils/integrity_events.py</t>
         </is>
       </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>STORY-35.2; STORY-37.10; STORY-37.12; STORY-37.13; STORY-38.2</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
@@ -43371,6 +47000,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>STORY-38.3</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
@@ -43449,6 +47083,11 @@
           <t>src/config_layer/production_config.py; src/utils/logging_config.py</t>
         </is>
       </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>STORY-29.2</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="inlineStr">
@@ -43644,6 +47283,11 @@
           <t>locale</t>
         </is>
       </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>STORY-14.1; STORY-18.12; STORY-20.5; STORY-23.8; STORY-29.1; STORY-30.2; STORY-33.5; STORY-38.6; STORY-41.13; STORY-41.34; STORY-41.38</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
@@ -43683,6 +47327,11 @@
           <t>src/events/event_fabric.py</t>
         </is>
       </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-21.1; STORY-25.32; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
@@ -43722,6 +47371,11 @@
           <t>src/events/event_fabric.py</t>
         </is>
       </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>STORY-20.4; STORY-21.2</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" s="2" t="inlineStr">
@@ -43761,6 +47415,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-16.5; STORY-25.32; STORY-30.4; STORY-32.2; STORY-38.2; STORY-38.3; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" s="2" t="inlineStr">
@@ -43800,6 +47459,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>STORY-32.1</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
@@ -43839,6 +47503,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
@@ -43878,6 +47547,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>STORY-14.10</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -43917,6 +47591,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>STORY-14.10</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
@@ -43956,6 +47635,11 @@
           <t>src/utils/console_safe.py</t>
         </is>
       </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-18.11; STORY-18.12; STORY-29.2; STORY-38.6</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
@@ -43995,6 +47679,11 @@
           <t>src/utils/jsonl_writer.py</t>
         </is>
       </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>STORY-25.4; STORY-25.6; STORY-25.14; STORY-25.24; STORY-41.30; STORY-41.40; STORY-41.44; STORY-44.1</t>
+        </is>
+      </c>
     </row>
     <row r="942">
       <c r="A942" s="2" t="inlineStr">
@@ -44034,6 +47723,11 @@
           <t>src/config_layer/crt_engine_v2.py</t>
         </is>
       </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>STORY-18.11; STORY-20.4</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" s="2" t="inlineStr">
@@ -44112,6 +47806,11 @@
           <t>src/config_layer/production_config.py</t>
         </is>
       </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-31.4</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" s="2" t="inlineStr">
@@ -44151,6 +47850,11 @@
           <t>src/events/event_fabric.py</t>
         </is>
       </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>STORY-21.2</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" s="2" t="inlineStr">
@@ -44190,6 +47894,11 @@
           <t>src/events/event_fabric.py</t>
         </is>
       </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>STORY-14.10; STORY-21.1; STORY-21.2; STORY-30.5; STORY-35.2</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="2" t="inlineStr">
@@ -44229,6 +47938,11 @@
           <t>(none / stdlib-only)</t>
         </is>
       </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>STORY-14.4; STORY-31.4</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" s="2" t="inlineStr">
@@ -44266,6 +47980,11 @@
       <c r="I948" s="2" t="inlineStr">
         <is>
           <t>(none / stdlib-only)</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>STORY-18.12</t>
         </is>
       </c>
     </row>
@@ -57309,7 +61028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -57484,6 +61203,18 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Story_IDs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>build_queue.jsonl stories whose files list names this file (added 2026-09-17)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
